--- a/data/rutinas/sucursales/Socios_con_y_sin_rutina__INSURGENTES.xlsx
+++ b/data/rutinas/sucursales/Socios_con_y_sin_rutina__INSURGENTES.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC23"/>
+  <dimension ref="A1:AC39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,12 +578,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>347446</t>
+          <t>347322</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>89611</t>
+          <t>89487</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -593,17 +593,17 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>CELIA</t>
+          <t xml:space="preserve">OSCAR DANIEL </t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">RUIZ </t>
+          <t xml:space="preserve">HERNANDEZ </t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>BAEZ</t>
+          <t>CARRIZOSA</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -613,28 +613,28 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>5534529869</t>
+          <t>2217188025</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>03-02-1947</t>
+          <t>13-02-1997</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>BARUCE03@GMAIL.COM</t>
+          <t>OSHESIER77@GMAIL.COM</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>02-03-2026 08:33:45</t>
+          <t>01-03-2026 11:37:19</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -644,36 +644,44 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>ANUALIDAD + MES REGALO $6,999</t>
+          <t>DOMICILIADO 12 MESES $649 HE</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>538.38</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>02-03-2026 15:13:40</t>
+          <t>01-03-2026 11:46:48</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>02-04-2027 23:59:59</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr"/>
+          <t>01-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>01-03-2026 11:46:09</t>
+        </is>
+      </c>
       <c r="U2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr"/>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W2" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -681,36 +689,36 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>26280522796960008056</t>
+          <t>26280522768240007896</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr"/>
       <c r="Z2" t="inlineStr"/>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>6999</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Josue Radames Rosales Rojas</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>347322</t>
+          <t>345774</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>89487</t>
+          <t>87939</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -720,17 +728,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">OSCAR DANIEL </t>
+          <t>SASKIA</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">HERNANDEZ </t>
+          <t>TOMPSETT</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>CARRIZOSA</t>
+          <t>TOMPSETT</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -740,28 +748,28 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2217188025</t>
+          <t>5665883237</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>13-02-1997</t>
+          <t>11-06-1991</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>OSHESIER77@GMAIL.COM</t>
+          <t>SASKIATOMPSETT@GMAIL.COM</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>01-03-2026 11:37:19</t>
+          <t>23-02-2026 13:32:52</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -771,44 +779,36 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $649 HE</t>
+          <t>1 MES $999</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>999</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>01-03-2026 11:46:48</t>
+          <t>02-03-2026 09:11:50</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>01-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>01-03-2026 11:46:09</t>
-        </is>
-      </c>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V3" t="inlineStr"/>
       <c r="W3" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -816,36 +816,40 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>26280522768240007896</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr"/>
+          <t>26280522785380007960</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
       <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>999</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>Josue Radames Rosales Rojas</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>347033</t>
+          <t>347283</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>89198</t>
+          <t>89448</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -855,17 +859,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">VALERIA ALEJANDRA </t>
+          <t xml:space="preserve">AXEL ANTONIO </t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">PADILLA </t>
+          <t xml:space="preserve">HERRERA </t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASE </t>
+          <t xml:space="preserve">RUIZ </t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -875,14 +879,10 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>5512118910</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>TLALPAN</t>
-        </is>
-      </c>
+          <t>8332617094</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -890,17 +890,17 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>03-02-2006</t>
+          <t>26-12-1997</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>VALERIACASEPER@GMAIL.COM</t>
+          <t>AXELHERREARUIZ@GMAIL.COM</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>27-02-2026 17:40:59</t>
+          <t>01-03-2026 09:27:23</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -910,22 +910,22 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>CONVENIO DOMICILIADO $549</t>
+          <t>1 MES $999</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>999</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>01-03-2026 13:25:12</t>
+          <t>01-03-2026 09:32:48</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -933,21 +933,13 @@
           <t>01-04-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>01-03-2026 13:23:47</t>
-        </is>
-      </c>
+      <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V4" t="inlineStr"/>
       <c r="W4" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -955,14 +947,14 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>26280522769860007910</t>
+          <t>26280522765690007884</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr"/>
       <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>999</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -979,12 +971,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>347371</t>
+          <t>347338</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>89536</t>
+          <t>89503</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -994,17 +986,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>ALBERTO</t>
+          <t xml:space="preserve">JAIR JOCSAN </t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">ORTIGOZA </t>
+          <t>YBARRA</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>PEREZ</t>
+          <t xml:space="preserve">CORTES </t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1014,12 +1006,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>5649112537</t>
+          <t>5971145759</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>HERRERIAS</t>
+          <t>TLALPAN</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1029,17 +1021,17 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>14-11-2013</t>
+          <t>24-06-1996</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>ALBERTOOGAZA@GMAIL.COM</t>
+          <t>JAIRIBACOR@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>02-03-2026 04:30:26</t>
+          <t>01-03-2026 12:27:06</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -1054,27 +1046,27 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>CONVENIO DOMICILIADO $549</t>
+          <t>PLAN RECURRENTE PAGO INCIAL $1,549 HE</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>1549</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>02-03-2026 04:40:19</t>
+          <t>01-03-2026 12:41:08</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>02-03-2026 04:39:54</t>
+          <t>01-03-2026 12:40:23</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -1084,7 +1076,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1094,14 +1086,14 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>26280522772000007922</t>
+          <t>26280522769240007906</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr"/>
       <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>1549</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -1118,12 +1110,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>347565</t>
+          <t>347164</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>89730</t>
+          <t>89329</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1133,17 +1125,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>JESUS MIGUEL</t>
+          <t>ALMA LIZET</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>LUNA</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>VILLEGAS</t>
+          <t>ARENAS</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1153,7 +1145,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2223618726</t>
+          <t>5561052467</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1163,22 +1155,22 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>07-05-1994</t>
+          <t>14-10-1975</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>MIGUEL_LV94@HOTMAIL.COM</t>
+          <t>ALMAARENAS777@GMAIL.COM</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>02-03-2026 13:29:01</t>
+          <t>28-02-2026 09:37:15</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1188,12 +1180,12 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>PLAN RECURRENTE PAGO INCIAL $1,549 HE</t>
+          <t>DOMICILIADO PLAN ULTRA PAGO INCIAL 12 MESES $1,549 HE</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -1203,17 +1195,17 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>02-03-2026 13:35:29</t>
+          <t>03-03-2026 14:29:23</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>03-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>02-03-2026 13:34:42</t>
+          <t>03-03-2026 14:28:32</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1223,7 +1215,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1233,10 +1225,14 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>26280522793220008032</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr"/>
+          <t>26280522841740008298</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
       <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="inlineStr">
         <is>
@@ -1245,24 +1241,24 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>Diana Itzel Martinez Colín</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>347569</t>
+          <t>347033</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>89734</t>
+          <t>89198</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1272,17 +1268,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>YURIDIA</t>
+          <t xml:space="preserve">VALERIA ALEJANDRA </t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>ROMAN</t>
+          <t xml:space="preserve">PADILLA </t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>LAUREL</t>
+          <t xml:space="preserve">CASE </t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1292,7 +1288,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>7444494140</t>
+          <t>5512118910</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1307,17 +1303,17 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>15-09-1972</t>
+          <t>03-02-2006</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>YURISLIRIS@YAHOO.COM</t>
+          <t>VALERIACASEPER@GMAIL.COM</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>02-03-2026 13:33:31</t>
+          <t>27-02-2026 17:40:59</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1342,17 +1338,17 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>02-03-2026 13:42:53</t>
+          <t>01-03-2026 13:25:12</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>02-03-2026 13:40:35</t>
+          <t>01-03-2026 13:23:47</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1372,7 +1368,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>26280522793430008035</t>
+          <t>26280522769860007910</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr"/>
@@ -1396,12 +1392,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>345774</t>
+          <t>346388</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>87939</t>
+          <t>88553</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1411,17 +1407,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>SASKIA</t>
+          <t xml:space="preserve">RAISA ITZEL </t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>TOMPSETT</t>
+          <t xml:space="preserve">MONTERO </t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>TOMPSETT</t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1431,10 +1427,14 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>5665883237</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>5528002913</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>TLALPAN</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -1442,17 +1442,17 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>11-06-1991</t>
+          <t>22-02-1988</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>SASKIATOMPSETT@GMAIL.COM</t>
+          <t>RAISAMONTEROMARTINEZ@GMAIL.COM</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>23-02-2026 13:32:52</t>
+          <t>25-02-2026 08:43:52</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1462,36 +1462,44 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>1 MES $999</t>
+          <t>PLAN RECURRENTE PAGO INCIAL $1,549 HE</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>999</t>
+          <t>1549</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>02-03-2026 09:11:50</t>
+          <t>01-03-2026 12:36:04</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr"/>
+          <t>01-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>01-03-2026 12:35:15</t>
+        </is>
+      </c>
       <c r="U8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr"/>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W8" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1499,18 +1507,14 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>26280522785380007960</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS WEB</t>
-        </is>
-      </c>
+          <t>26280522769120007905</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr"/>
       <c r="Z8" t="inlineStr"/>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>999</t>
+          <t>1549</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -1527,12 +1531,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>347283</t>
+          <t>347046</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>89448</t>
+          <t>89211</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1542,17 +1546,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">AXEL ANTONIO </t>
+          <t>GIOVANNA</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">HERRERA </t>
+          <t>FREGOSO</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t xml:space="preserve">RUIZ </t>
+          <t>BARRERA</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1562,7 +1566,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>8332617094</t>
+          <t>4428692086</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1573,17 +1577,17 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>26-12-1997</t>
+          <t>02-10-2002</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>AXELHERREARUIZ@GMAIL.COM</t>
+          <t>GIOVANNAFREGOSO269@GMAIL.COM</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>01-03-2026 09:27:23</t>
+          <t>27-02-2026 18:08:30</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1593,36 +1597,44 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>1 MES $999</t>
+          <t>CONVENIO DOMICILIADO $549</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>999</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>01-03-2026 09:32:48</t>
+          <t>03-03-2026 18:38:08</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>01-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr"/>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>03-03-2026 18:37:34</t>
+        </is>
+      </c>
       <c r="U9" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr"/>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W9" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1630,14 +1642,18 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>26280522765690007884</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr"/>
+          <t>26280522855830008380</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
       <c r="Z9" t="inlineStr"/>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>999</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -1654,12 +1670,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>347338</t>
+          <t>347759</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>89503</t>
+          <t>89924</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1669,17 +1685,17 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">JAIR JOCSAN </t>
+          <t>CARLOS</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>YBARRA</t>
+          <t xml:space="preserve">MARTINEZ </t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t xml:space="preserve">CORTES </t>
+          <t>ZARZA</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1689,7 +1705,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>5971145759</t>
+          <t>5517473620</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1704,17 +1720,17 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>24-06-1996</t>
+          <t>24-03-1984</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>JAIRIBACOR@HOTMAIL.COM</t>
+          <t>EMZARZA4@GMAIL.COM</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>01-03-2026 12:27:06</t>
+          <t>02-03-2026 17:40:33</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1724,12 +1740,12 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>PLAN RECURRENTE PAGO INCIAL $1,549 HE</t>
+          <t>DOMICILIADO PLAN ULTRA PAGO INCIAL 12 MESES $1,549 HE</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
@@ -1739,17 +1755,17 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>01-03-2026 12:41:08</t>
+          <t>02-03-2026 17:52:53</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>01-04-2026 23:59:59</t>
+          <t>02-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>01-03-2026 12:40:23</t>
+          <t>02-03-2026 17:52:23</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1769,7 +1785,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>26280522769240007906</t>
+          <t>26280522808850008128</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr"/>
@@ -1793,12 +1809,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>347759</t>
+          <t>347981</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>89924</t>
+          <t>90146</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1808,17 +1824,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>CARLOS</t>
+          <t xml:space="preserve">VALERIA </t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">MARTINEZ </t>
+          <t>RUIZ</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ZARZA</t>
+          <t>MACIAS</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1828,32 +1844,32 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>5517473620</t>
+          <t>5571120475</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>TLALPAN</t>
+          <t>COL SAN JUAN DE ARAGON</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>24-03-1984</t>
+          <t>16-07-2004</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>EMZARZA4@GMAIL.COM</t>
+          <t>VALERIA.A.RUIZ@OUTLOOK.COM</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>02-03-2026 17:40:33</t>
+          <t>03-03-2026 09:02:04</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1863,32 +1879,32 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>DOMICILIADO PLAN ULTRA PAGO INCIAL 12 MESES $1,549 HE</t>
+          <t>CONVENIO DOMICILIADO $549</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>1549</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>02-03-2026 17:52:53</t>
+          <t>03-03-2026 09:15:14</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>03-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>02-03-2026 17:52:23</t>
+          <t>03-03-2026 09:12:40</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1908,24 +1924,24 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>26280522808850008128</t>
+          <t>26280522834570008225</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr"/>
       <c r="Z11" t="inlineStr"/>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>1549</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Josue Radames Rosales Rojas</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
@@ -2075,12 +2091,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>346388</t>
+          <t>347371</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>88553</t>
+          <t>89536</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2090,17 +2106,17 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">RAISA ITZEL </t>
+          <t>ALBERTO</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">MONTERO </t>
+          <t xml:space="preserve">ORTIGOZA </t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t>PEREZ</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -2110,32 +2126,32 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>5528002913</t>
+          <t>5649112537</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>TLALPAN</t>
+          <t>HERRERIAS</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>22-02-1988</t>
+          <t>14-11-2013</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>RAISAMONTEROMARTINEZ@GMAIL.COM</t>
+          <t>ALBERTOOGAZA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>25-02-2026 08:43:52</t>
+          <t>02-03-2026 04:30:26</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -2150,27 +2166,27 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>PLAN RECURRENTE PAGO INCIAL $1,549 HE</t>
+          <t>CONVENIO DOMICILIADO $549</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>1549</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>01-03-2026 12:36:04</t>
+          <t>02-03-2026 04:40:19</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>01-04-2026 23:59:59</t>
+          <t>02-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>01-03-2026 12:35:15</t>
+          <t>02-03-2026 04:39:54</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -2180,7 +2196,7 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
@@ -2190,14 +2206,14 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>26280522769120007905</t>
+          <t>26280522772000007922</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr"/>
       <c r="Z13" t="inlineStr"/>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>1549</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -2214,12 +2230,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>347674</t>
+          <t>347680</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>89839</t>
+          <t>89845</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2229,17 +2245,17 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>ARMANDO</t>
+          <t>ARTURO</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>ARCOS</t>
+          <t>HERNANDEZ</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>MARTINES</t>
+          <t>MAGALLON</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -2249,14 +2265,10 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>4811008585</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>TLALPAN</t>
-        </is>
-      </c>
+          <t>5610667660</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -2264,17 +2276,17 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>28-08-1997</t>
+          <t>14-11-1975</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>MEDICINAUASLP13@HOTMAIL.COM</t>
+          <t>HE.MAGALLON@GMAIL.COM</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>02-03-2026 16:28:39</t>
+          <t>02-03-2026 16:35:10</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -2284,44 +2296,36 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $649 HE</t>
+          <t>1 MES $999</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>999</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>02-03-2026 17:40:11</t>
+          <t>02-03-2026 16:46:28</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>02-03-2026 17:39:26</t>
-        </is>
-      </c>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr"/>
       <c r="U14" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V14" t="inlineStr"/>
       <c r="W14" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2329,22 +2333,14 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>26280522807450008117</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>Gabriel Pacheco Sanchez</t>
-        </is>
-      </c>
+          <t>26280522803020008099</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>999</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -2361,12 +2357,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>347680</t>
+          <t>347482</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>89845</t>
+          <t>89647</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2376,17 +2372,17 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>ARTURO</t>
+          <t>DAVID</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>HERNANDEZ</t>
+          <t>LLANOS</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>MAGALLON</t>
+          <t>LEGORRETA</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -2396,10 +2392,14 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>5610667660</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>5620518609</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>PLUTARCO ELIAS CALLES</t>
+        </is>
+      </c>
       <c r="J15" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -2407,17 +2407,17 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>14-11-1975</t>
+          <t>07-04-1974</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>HE.MAGALLON@GMAIL.COM</t>
+          <t>DAVIDLEGORRETA@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>02-03-2026 16:35:10</t>
+          <t>02-03-2026 10:20:10</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -2427,36 +2427,44 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>1 MES $999</t>
+          <t>DOMICILIADO 12 MESES $649 HE</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>999</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>02-03-2026 16:46:28</t>
+          <t>03-03-2026 04:33:30</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr"/>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>03-03-2026 04:29:55</t>
+        </is>
+      </c>
       <c r="U15" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V15" t="inlineStr"/>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W15" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2464,14 +2472,14 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>26280522803020008099</t>
+          <t>26280522822310008190</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr"/>
       <c r="Z15" t="inlineStr"/>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>999</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -2488,12 +2496,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>347604</t>
+          <t>347565</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>89769</t>
+          <t>89730</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2503,17 +2511,17 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">ALEXIS </t>
+          <t>JESUS MIGUEL</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>CABRERA</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>GONZALEZ</t>
+          <t>VILLEGAS</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -2523,7 +2531,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>5573598515</t>
+          <t>2223618726</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2538,17 +2546,17 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>09-04-2005</t>
+          <t>07-05-1994</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>ALEXBORRE2005@GMAIL.COM</t>
+          <t>MIGUEL_LV94@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>02-03-2026 14:48:34</t>
+          <t>02-03-2026 13:29:01</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -2563,17 +2571,17 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>CONVENIO DOMICILIADO $549</t>
+          <t>PLAN RECURRENTE PAGO INCIAL $1,549 HE</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>1549</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>02-03-2026 17:06:11</t>
+          <t>02-03-2026 13:35:29</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2583,7 +2591,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>02-03-2026 17:05:43</t>
+          <t>02-03-2026 13:34:42</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2593,7 +2601,7 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
@@ -2603,36 +2611,36 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>26280522804840008105</t>
+          <t>26280522793220008032</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr"/>
       <c r="Z16" t="inlineStr"/>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>1549</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Diana Itzel Martinez Colín</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>347777</t>
+          <t>347569</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>89942</t>
+          <t>89734</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2642,17 +2650,17 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>CHRISTIAN IVAN</t>
+          <t>YURIDIA</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>MERUBIA</t>
+          <t>ROMAN</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>NAVIA</t>
+          <t>LAUREL</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2662,7 +2670,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>5611521821</t>
+          <t>7444494140</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2672,22 +2680,22 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>19-10-1992</t>
+          <t>15-09-1972</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>CHRIS_MERUBIA@HOTMAIL.COM</t>
+          <t>YURISLIRIS@YAHOO.COM</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>02-03-2026 17:55:56</t>
+          <t>02-03-2026 13:33:31</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -2697,32 +2705,32 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $649 HE</t>
+          <t>CONVENIO DOMICILIADO $549</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>02-03-2026 19:27:30</t>
+          <t>02-03-2026 13:42:53</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>02-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>02-03-2026 19:26:52</t>
+          <t>02-03-2026 13:40:35</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2742,18 +2750,14 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>26280522816680008169</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS WEB</t>
-        </is>
-      </c>
+          <t>26280522793430008035</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr"/>
       <c r="Z17" t="inlineStr"/>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -2770,12 +2774,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>347685</t>
+          <t>347674</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>89850</t>
+          <t>89839</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2785,17 +2789,17 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NAHOMI</t>
+          <t>ARMANDO</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>CABRERA</t>
+          <t>ARCOS</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>GONZALEZ</t>
+          <t>MARTINES</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2805,7 +2809,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>5559971564</t>
+          <t>4811008585</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2815,22 +2819,22 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>29-06-2000</t>
+          <t>28-08-1997</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>NAHOMICABRERAG.29@GMAIL.COM</t>
+          <t>MEDICINAUASLP13@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>02-03-2026 16:37:42</t>
+          <t>02-03-2026 16:28:39</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2845,27 +2849,27 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>DOMICILIADO PLAN ULTRA PAGO INCIAL 12 MESES $1,549 HE</t>
+          <t>DOMICILIADO 12 MESES $649 HE</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>1549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>02-03-2026 16:58:55</t>
+          <t>02-03-2026 17:40:11</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>03-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>02-03-2026 16:57:34</t>
+          <t>02-03-2026 17:39:26</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2885,14 +2889,22 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>26280522804160008103</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr"/>
-      <c r="Z18" t="inlineStr"/>
+          <t>26280522807450008117</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>Gabriel Pacheco Sanchez</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>1549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -2909,12 +2921,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>347715</t>
+          <t>347604</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>89880</t>
+          <t>89769</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2924,17 +2936,17 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>EDUARDO LOPEZ</t>
+          <t xml:space="preserve">ALEXIS </t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t xml:space="preserve">LOPEZ </t>
+          <t>CABRERA</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t xml:space="preserve">SANTANA </t>
+          <t>GONZALEZ</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2944,12 +2956,12 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>5530598571</t>
+          <t>5573598515</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t xml:space="preserve">TLALPAN </t>
+          <t>TLALPAN</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2959,17 +2971,17 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>04-01-2001</t>
+          <t>09-04-2005</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>EDUARDOLOPEZSANTANA1A@GMAIL.COM</t>
+          <t>ALEXBORRE2005@GMAIL.COM</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>02-03-2026 17:02:13</t>
+          <t>02-03-2026 14:48:34</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -2984,17 +2996,17 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>RECURRENTE $799 HE</t>
+          <t>CONVENIO DOMICILIADO $549</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>02-03-2026 17:14:28</t>
+          <t>02-03-2026 17:06:11</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -3004,7 +3016,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>02-03-2026 17:09:16</t>
+          <t>02-03-2026 17:05:43</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -3024,14 +3036,14 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>26280522805500008106</t>
+          <t>26280522804840008105</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr"/>
       <c r="Z19" t="inlineStr"/>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -3048,12 +3060,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>347583</t>
+          <t>347777</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>89748</t>
+          <t>89942</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -3063,17 +3075,17 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>JUAN SALVADOR</t>
+          <t>CHRISTIAN IVAN</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>PEREZ</t>
+          <t>MERUBIA</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>CASTRO</t>
+          <t>NAVIA</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -3083,32 +3095,32 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>5527670454</t>
+          <t>5611521821</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>INSURGENTES SUR</t>
+          <t>TLALPAN</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>23-01-1985</t>
+          <t>19-10-1992</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>JUANITZIO04@GMAIL.COM</t>
+          <t>CHRIS_MERUBIA@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>02-03-2026 14:08:29</t>
+          <t>02-03-2026 17:55:56</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -3123,27 +3135,27 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>DOMICILIADO PLAN ULTRA PAGO INCIAL 12 MESES $1,549 HE</t>
+          <t>DOMICILIADO 12 MESES $649 HE</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>1549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>02-03-2026 14:20:01</t>
+          <t>02-03-2026 19:27:30</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>03-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>02-03-2026 14:15:35</t>
+          <t>02-03-2026 19:26:52</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -3153,7 +3165,7 @@
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
@@ -3163,14 +3175,18 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>26280522794490008042</t>
-        </is>
-      </c>
-      <c r="Y20" t="inlineStr"/>
+          <t>26280522816680008169</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
       <c r="Z20" t="inlineStr"/>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>1549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -3187,12 +3203,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>347557</t>
+          <t>347503</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>89722</t>
+          <t>89668</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -3202,17 +3218,17 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>SANTIAGO</t>
+          <t xml:space="preserve">ENDRID </t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t xml:space="preserve">MORALES </t>
+          <t>BELTRAN</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>ALEJANDRO</t>
+          <t>VAZQUEZ</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -3222,10 +3238,14 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>5565099868</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>5565644393</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>INSURGENTES SUR</t>
+        </is>
+      </c>
       <c r="J21" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -3233,17 +3253,17 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>19-12-2008</t>
+          <t>13-07-2005</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>ALECOLATE2009@GMAIL.COM</t>
+          <t>YAMILEMF8@GMAIL.COM</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>02-03-2026 13:11:52</t>
+          <t>02-03-2026 11:18:02</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -3253,12 +3273,12 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>CONVENIO DOMICILIADO $549</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
@@ -3268,21 +3288,29 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>02-03-2026 15:09:04</t>
+          <t>03-03-2026 11:36:28</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T21" t="inlineStr"/>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>03-03-2026 11:33:50</t>
+        </is>
+      </c>
       <c r="U21" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V21" t="inlineStr"/>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W21" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3290,7 +3318,7 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>26280522796610008055</t>
+          <t>26280522837720008249</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr"/>
@@ -3314,12 +3342,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>347613</t>
+          <t>347583</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>89778</t>
+          <t>89748</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3329,30 +3357,34 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>RAQUEL</t>
+          <t>JUAN SALVADOR</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>MONEGRO</t>
+          <t>PEREZ</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>CORDERO</t>
+          <t>CASTRO</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>52</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>1809953468</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>5527670454</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>INSURGENTES SUR</t>
+        </is>
+      </c>
       <c r="J22" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -3360,17 +3392,17 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>28-12-1994</t>
+          <t>23-01-1985</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>MONEGREORAQUEL@GMAIL.COM</t>
+          <t>JUANITZIO04@GMAIL.COM</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>02-03-2026 15:00:46</t>
+          <t>02-03-2026 14:08:29</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -3380,22 +3412,22 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>1 MES $999</t>
+          <t>DOMICILIADO PLAN ULTRA PAGO INCIAL 12 MESES $1,549 HE</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>999</t>
+          <t>1549</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>02-03-2026 15:03:20</t>
+          <t>02-03-2026 14:20:01</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -3403,13 +3435,21 @@
           <t>02-04-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T22" t="inlineStr"/>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>02-03-2026 14:15:35</t>
+        </is>
+      </c>
       <c r="U22" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V22" t="inlineStr"/>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W22" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3417,14 +3457,14 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>26280522796360008051</t>
+          <t>26280522794490008042</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr"/>
       <c r="Z22" t="inlineStr"/>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>999</t>
+          <t>1549</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -3441,12 +3481,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>347566</t>
+          <t>347557</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>89731</t>
+          <t>89722</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3456,17 +3496,17 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>ERIC</t>
+          <t>SANTIAGO</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t xml:space="preserve">MORALES </t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>ROMAN</t>
+          <t>ALEJANDRO</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -3476,14 +3516,10 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>5540969149</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>TLALPAN</t>
-        </is>
-      </c>
+          <t>5565099868</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -3491,17 +3527,17 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>08-08-2008</t>
+          <t>19-12-2008</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>ERICSAN08@GMAIL.COM</t>
+          <t>ALECOLATE2009@GMAIL.COM</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>02-03-2026 13:30:16</t>
+          <t>02-03-2026 13:11:52</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -3511,12 +3547,12 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>CONVENIO DOMICILIADO $549</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
@@ -3526,7 +3562,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>02-03-2026 13:48:48</t>
+          <t>02-03-2026 15:09:04</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -3534,21 +3570,13 @@
           <t>02-04-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T23" t="inlineStr">
-        <is>
-          <t>02-03-2026 13:45:33</t>
-        </is>
-      </c>
+      <c r="T23" t="inlineStr"/>
       <c r="U23" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V23" t="inlineStr"/>
       <c r="W23" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3556,7 +3584,7 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>26280522793620008038</t>
+          <t>26280522796610008055</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr"/>
@@ -3574,6 +3602,2166 @@
       <c r="AC23" t="inlineStr">
         <is>
           <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>347613</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>89778</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>INSURGENTES</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>RAQUEL</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>MONEGRO</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>CORDERO</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>1809953468</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>28-12-1994</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>MONEGREORAQUEL@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>02-03-2026 15:00:46</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 HE</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>1 MES $999</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>02-03-2026 15:03:20</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr"/>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>26280522796360008051</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr"/>
+      <c r="Z24" t="inlineStr"/>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>347446</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>89611</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>INSURGENTES</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>CELIA</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RUIZ </t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>BAEZ</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>5534529869</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>03-02-1947</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>BARUCE03@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>02-03-2026 08:33:45</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 HE</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>ANUALIDAD + MES REGALO $6,999</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>538.38</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>02-03-2026 15:13:40</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>02-04-2027 23:59:59</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr"/>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr"/>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>26280522796960008056</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr"/>
+      <c r="Z25" t="inlineStr"/>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>6999</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>347685</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>89850</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>INSURGENTES</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NAHOMI</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>CABRERA</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>GONZALEZ</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>5559971564</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>TLALPAN</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>29-06-2000</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>NAHOMICABRERAG.29@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>02-03-2026 16:37:42</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 HE</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>DOMICILIADO PLAN ULTRA PAGO INCIAL 12 MESES $1,549 HE</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>1549</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>02-03-2026 16:58:55</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>02-03-2026 16:57:34</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>26280522804160008103</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr"/>
+      <c r="Z26" t="inlineStr"/>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>1549</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>347715</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>89880</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>INSURGENTES</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>EDUARDO LOPEZ</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LOPEZ </t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SANTANA </t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>5530598571</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TLALPAN </t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>04-01-2001</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>EDUARDOLOPEZSANTANA1A@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>02-03-2026 17:02:13</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 HE</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>RECURRENTE $799 HE</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>799</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>02-03-2026 17:14:28</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>02-03-2026 17:09:16</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>26280522805500008106</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr"/>
+      <c r="Z27" t="inlineStr"/>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>799</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>348081</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>90246</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>INSURGENTES</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NATALIA </t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SANCHEZ </t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>MENDOZA</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>5545290873</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>TLALPAN</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>29-08-2007</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>NATALIAMENDOZA790101@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>03-03-2026 15:19:31</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 HE</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>DOMICILIADO PLAN ULTRA PAGO INCIAL 12 MESES $1,549 HE</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>1549</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>03-03-2026 15:29:19</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>03-03-2026 15:28:33</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>26280522843920008315</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr"/>
+      <c r="Z28" t="inlineStr"/>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>1549</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>348134</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>90299</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>INSURGENTES</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>PABLO ANGEL</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CARRILLO </t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>JUAREZ</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>5544502085</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>12-10-1998</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>PABLOACARRILLOJ@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>03-03-2026 16:49:36</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 HE</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>03-03-2026 16:58:26</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr"/>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr"/>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>26280522848750008333</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr"/>
+      <c r="Z29" t="inlineStr"/>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>348207</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>90372</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>INSURGENTES</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>YESELMI EMELIN</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BRIVIESCA </t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MEJIA </t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>5581061114</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>27-08-2007</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>BRIVIESCAYUSLEMI@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>03-03-2026 18:00:26</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 HE</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>CONVENIO DOMICILIADO $549</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>03-03-2026 18:19:14</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>03-03-2026 18:18:38</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>26280522854400008370</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr"/>
+      <c r="Z30" t="inlineStr"/>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>348009</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>90174</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>INSURGENTES</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">KEVIN </t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>OSORIA</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>CORTINAS</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>8662568650</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>11-01-2003</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>KEVINOSORIA57@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>03-03-2026 11:14:35</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 HE</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>03-03-2026 11:30:05</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr"/>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr"/>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>26280522837550008246</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr"/>
+      <c r="Z31" t="inlineStr"/>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>Diana Itzel Martinez Colín</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>348141</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>90306</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>INSURGENTES</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>BERTHA MARIA</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BALDERAS </t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>ARENAS</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>5554577198</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>17-01-1971</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>BERTHACAMPERO@YAHOO.COM</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>03-03-2026 17:00:25</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 HE</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $649 HE</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>03-03-2026 17:10:00</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>03-03-2026 17:09:07</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>26280522849360008343</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr"/>
+      <c r="Z32" t="inlineStr"/>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>Omar Carillo Leal</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>348179</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>90344</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>INSURGENTES</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ANDREA </t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NICOLAS </t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FLORES </t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>5561653454</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>TLALPAN</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>05-04-1999</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>NIFAANDREA@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>03-03-2026 17:32:31</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 HE</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>DOMICILIADO PLAN ULTRA PAGO INCIAL 12 MESES $1,549 HE</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>1549</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>03-03-2026 17:42:08</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>03-03-2026 17:41:31</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>26280522851620008359</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr"/>
+      <c r="Z33" t="inlineStr"/>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>1549</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>348273</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>90438</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>INSURGENTES</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JERONIMO </t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SOTO </t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ORTEGA </t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>5567035457</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>TLALPAN</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>12-10-1992</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>MOMO851245@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>03-03-2026 19:34:21</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 HE</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $649 HE</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>03-03-2026 19:43:09</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>03-03-2026 19:42:28</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>26280522859660008404</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr"/>
+      <c r="Z34" t="inlineStr"/>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>348270</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>90435</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>INSURGENTES</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BRENDA </t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VALLE </t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VILLEGAS </t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>5528942610</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>TLALPAN</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>16-04-1998</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>BRE160498V@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>03-03-2026 19:31:08</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 HE</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $649 HE</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>03-03-2026 19:40:05</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>03-03-2026 19:39:01</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>26280522859590008403</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr"/>
+      <c r="Z35" t="inlineStr"/>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>347566</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>89731</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>INSURGENTES</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>ERIC</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>SANCHEZ</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>ROMAN</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>5540969149</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>TLALPAN</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>08-08-2008</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>ERICSAN08@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>02-03-2026 13:30:16</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 HE</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>CONVENIO DOMICILIADO $549</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>02-03-2026 13:48:48</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>02-03-2026 13:45:33</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>26280522793620008038</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr"/>
+      <c r="Z36" t="inlineStr"/>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>348189</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>90354</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>INSURGENTES</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MATEO </t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SUAREZ </t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PICHARDO </t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>5633352915</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>02-12-2010</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>MATEO.SUAREZ0212@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>03-03-2026 17:44:32</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 HE</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>CONVENIO DOMICILIADO $549</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>03-03-2026 18:00:56</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>03-03-2026 18:00:15</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>26280522853110008366</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr"/>
+      <c r="Z37" t="inlineStr"/>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>348071</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>90236</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>INSURGENTES</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>MIGUEL ANGEL</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FUENTES </t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>AVILA</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>3339470808</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>TLALPAN</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>29-09-1982</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>FUENTESAVILA82@YAHOO.COM.MX</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>03-03-2026 14:58:35</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 HE</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>RECURRENTE $799 HE</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>799</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>03-03-2026 15:07:01</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>03-03-2026 15:06:31</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>26280522843090008308</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr"/>
+      <c r="Z38" t="inlineStr"/>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>799</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>348119</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>90284</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>INSURGENTES</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LUIS ARMANDO </t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VILLA </t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CHAVEZ </t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>6143811757</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>14-06-1995</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>LUISARMANDOVILLAA@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>03-03-2026 16:29:37</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 HE</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $649 HE</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>03-03-2026 16:39:07</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>03-03-2026 16:38:32</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>26280522847410008326</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr"/>
+      <c r="Z39" t="inlineStr"/>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>Christian Yair Peña Villa</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>con rutina</t>
         </is>
       </c>
     </row>

--- a/data/rutinas/sucursales/Socios_con_y_sin_rutina__INSURGENTES.xlsx
+++ b/data/rutinas/sucursales/Socios_con_y_sin_rutina__INSURGENTES.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC39"/>
+  <dimension ref="A1:AC52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -713,12 +713,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>345774</t>
+          <t>347164</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>87939</t>
+          <t>89329</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -728,17 +728,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>SASKIA</t>
+          <t>ALMA LIZET</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>TOMPSETT</t>
+          <t>LUNA</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>TOMPSETT</t>
+          <t>ARENAS</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -748,10 +748,14 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>5665883237</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>5561052467</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>TLALPAN</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -759,17 +763,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>11-06-1991</t>
+          <t>14-10-1975</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>SASKIATOMPSETT@GMAIL.COM</t>
+          <t>ALMAARENAS777@GMAIL.COM</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>23-02-2026 13:32:52</t>
+          <t>28-02-2026 09:37:15</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -779,36 +783,44 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>1 MES $999</t>
+          <t>DOMICILIADO PLAN ULTRA PAGO INCIAL 12 MESES $1,549 HE</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>999</t>
+          <t>1549</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>02-03-2026 09:11:50</t>
+          <t>03-03-2026 14:29:23</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr"/>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>03-03-2026 14:28:32</t>
+        </is>
+      </c>
       <c r="U3" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr"/>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W3" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -816,7 +828,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>26280522785380007960</t>
+          <t>26280522841740008298</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -827,7 +839,7 @@
       <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>999</t>
+          <t>1549</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -844,12 +856,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>347283</t>
+          <t>342608</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>89448</t>
+          <t>20425</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -859,17 +871,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">AXEL ANTONIO </t>
+          <t>JAVIER ALEJANDRO</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">HERRERA </t>
+          <t>VERGARA</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t xml:space="preserve">RUIZ </t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -879,28 +891,32 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>8332617094</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>5624777884</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>TLALPAN</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>26-12-1997</t>
+          <t>19-10-2005</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>AXELHERREARUIZ@GMAIL.COM</t>
+          <t>JV986072@GMAIL.COM</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>01-03-2026 09:27:23</t>
+          <t>10-02-2026 13:12:12</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -910,36 +926,44 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>1 MES $999</t>
+          <t>DOMICILIADO 12 MESES $649 HE</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>999</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>01-03-2026 09:32:48</t>
+          <t>04-03-2026 15:13:27</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>01-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr"/>
+          <t>10-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>10-02-2026 13:17:13</t>
+        </is>
+      </c>
       <c r="U4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr"/>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W4" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -947,14 +971,14 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>26280522765690007884</t>
+          <t>26280522884670008529</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr"/>
       <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>999</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -971,12 +995,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>347338</t>
+          <t>345774</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>89503</t>
+          <t>87939</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -986,17 +1010,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">JAIR JOCSAN </t>
+          <t>SASKIA</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>YBARRA</t>
+          <t>TOMPSETT</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">CORTES </t>
+          <t>TOMPSETT</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1006,32 +1030,28 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>5971145759</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>TLALPAN</t>
-        </is>
-      </c>
+          <t>5665883237</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>24-06-1996</t>
+          <t>11-06-1991</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>JAIRIBACOR@HOTMAIL.COM</t>
+          <t>SASKIATOMPSETT@GMAIL.COM</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>01-03-2026 12:27:06</t>
+          <t>23-02-2026 13:32:52</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -1041,44 +1061,36 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>PLAN RECURRENTE PAGO INCIAL $1,549 HE</t>
+          <t>1 MES $999</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>1549</t>
+          <t>999</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>01-03-2026 12:41:08</t>
+          <t>02-03-2026 09:11:50</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>01-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>01-03-2026 12:40:23</t>
-        </is>
-      </c>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="V5" t="inlineStr"/>
       <c r="W5" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1086,14 +1098,18 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>26280522769240007906</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr"/>
+          <t>26280522785380007960</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
       <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>1549</t>
+          <t>999</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -1110,12 +1126,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>347164</t>
+          <t>344383</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>89329</t>
+          <t>22200</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1125,17 +1141,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>ALMA LIZET</t>
+          <t>YADIRA</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>LUNA</t>
+          <t>CORREA</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ARENAS</t>
+          <t>VILLEGAS</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1145,32 +1161,32 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>5561052467</t>
+          <t>5523151261</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>TLALPAN</t>
+          <t>C CORREGIDORA</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>14-10-1975</t>
+          <t>13-06-1977</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>ALMAARENAS777@GMAIL.COM</t>
+          <t>YCORREA@YAHOO.COM</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>28-02-2026 09:37:15</t>
+          <t>17-02-2026 06:42:07</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1180,32 +1196,32 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>DOMICILIADO PLAN ULTRA PAGO INCIAL 12 MESES $1,549 HE</t>
+          <t>CONVENIO DOMICILIADO $549</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>1549</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>03-03-2026 14:29:23</t>
+          <t>04-03-2026 04:56:30</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>04-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>03-03-2026 14:28:32</t>
+          <t>04-03-2026 04:53:54</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1215,7 +1231,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1225,7 +1241,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>26280522841740008298</t>
+          <t>26280522864040008421</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1236,7 +1252,7 @@
       <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>1549</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -1253,12 +1269,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>347033</t>
+          <t>347482</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>89198</t>
+          <t>89647</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1268,17 +1284,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">VALERIA ALEJANDRA </t>
+          <t>DAVID</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">PADILLA </t>
+          <t>LLANOS</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASE </t>
+          <t>LEGORRETA</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1288,32 +1304,32 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>5512118910</t>
+          <t>5620518609</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>TLALPAN</t>
+          <t>PLUTARCO ELIAS CALLES</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>03-02-2006</t>
+          <t>07-04-1974</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>VALERIACASEPER@GMAIL.COM</t>
+          <t>DAVIDLEGORRETA@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>27-02-2026 17:40:59</t>
+          <t>02-03-2026 10:20:10</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1323,32 +1339,32 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>CONVENIO DOMICILIADO $549</t>
+          <t>DOMICILIADO 12 MESES $649 HE</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>01-03-2026 13:25:12</t>
+          <t>03-03-2026 04:33:30</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>01-04-2026 23:59:59</t>
+          <t>03-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>01-03-2026 13:23:47</t>
+          <t>03-03-2026 04:29:55</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1368,14 +1384,14 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>26280522769860007910</t>
+          <t>26280522822310008190</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr"/>
       <c r="Z7" t="inlineStr"/>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -1392,12 +1408,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>346388</t>
+          <t>347565</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>88553</t>
+          <t>89730</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1407,17 +1423,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">RAISA ITZEL </t>
+          <t>JESUS MIGUEL</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">MONTERO </t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t>VILLEGAS</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1427,7 +1443,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>5528002913</t>
+          <t>2223618726</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1437,22 +1453,22 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>22-02-1988</t>
+          <t>07-05-1994</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>RAISAMONTEROMARTINEZ@GMAIL.COM</t>
+          <t>MIGUEL_LV94@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>25-02-2026 08:43:52</t>
+          <t>02-03-2026 13:29:01</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1477,17 +1493,17 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>01-03-2026 12:36:04</t>
+          <t>02-03-2026 13:35:29</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>01-04-2026 23:59:59</t>
+          <t>02-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>01-03-2026 12:35:15</t>
+          <t>02-03-2026 13:34:42</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1507,7 +1523,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>26280522769120007905</t>
+          <t>26280522793220008032</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr"/>
@@ -1519,24 +1535,24 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Diana Itzel Martinez Colín</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>347046</t>
+          <t>347569</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>89211</t>
+          <t>89734</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1546,17 +1562,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>GIOVANNA</t>
+          <t>YURIDIA</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>FREGOSO</t>
+          <t>ROMAN</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>BARRERA</t>
+          <t>LAUREL</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1566,10 +1582,14 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>4428692086</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>7444494140</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>TLALPAN</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -1577,17 +1597,17 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>02-10-2002</t>
+          <t>15-09-1972</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>GIOVANNAFREGOSO269@GMAIL.COM</t>
+          <t>YURISLIRIS@YAHOO.COM</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>27-02-2026 18:08:30</t>
+          <t>02-03-2026 13:33:31</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1612,17 +1632,17 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>03-03-2026 18:38:08</t>
+          <t>02-03-2026 13:42:53</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>02-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>03-03-2026 18:37:34</t>
+          <t>02-03-2026 13:40:35</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1642,14 +1662,10 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>26280522855830008380</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS WEB</t>
-        </is>
-      </c>
+          <t>26280522793430008035</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr"/>
       <c r="Z9" t="inlineStr"/>
       <c r="AA9" t="inlineStr">
         <is>
@@ -1670,12 +1686,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>347759</t>
+          <t>347283</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>89924</t>
+          <t>89448</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1685,17 +1701,17 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>CARLOS</t>
+          <t xml:space="preserve">AXEL ANTONIO </t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">MARTINEZ </t>
+          <t xml:space="preserve">HERRERA </t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ZARZA</t>
+          <t xml:space="preserve">RUIZ </t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1705,32 +1721,28 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>5517473620</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>TLALPAN</t>
-        </is>
-      </c>
+          <t>8332617094</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>24-03-1984</t>
+          <t>26-12-1997</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>EMZARZA4@GMAIL.COM</t>
+          <t>AXELHERREARUIZ@GMAIL.COM</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>02-03-2026 17:40:33</t>
+          <t>01-03-2026 09:27:23</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1740,44 +1752,36 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>DOMICILIADO PLAN ULTRA PAGO INCIAL 12 MESES $1,549 HE</t>
+          <t>1 MES $999</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>1549</t>
+          <t>999</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>02-03-2026 17:52:53</t>
+          <t>01-03-2026 09:32:48</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>02-03-2026 17:52:23</t>
-        </is>
-      </c>
+          <t>01-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr"/>
       <c r="U10" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="V10" t="inlineStr"/>
       <c r="W10" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1785,14 +1789,14 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>26280522808850008128</t>
+          <t>26280522765690007884</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr"/>
       <c r="Z10" t="inlineStr"/>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>1549</t>
+          <t>999</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -1809,12 +1813,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>347981</t>
+          <t>347338</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>90146</t>
+          <t>89503</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1824,17 +1828,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">VALERIA </t>
+          <t xml:space="preserve">JAIR JOCSAN </t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RUIZ</t>
+          <t>YBARRA</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>MACIAS</t>
+          <t xml:space="preserve">CORTES </t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1844,32 +1848,32 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>5571120475</t>
+          <t>5971145759</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>COL SAN JUAN DE ARAGON</t>
+          <t>TLALPAN</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>16-07-2004</t>
+          <t>24-06-1996</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>VALERIA.A.RUIZ@OUTLOOK.COM</t>
+          <t>JAIRIBACOR@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>03-03-2026 09:02:04</t>
+          <t>01-03-2026 12:27:06</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1884,27 +1888,27 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>CONVENIO DOMICILIADO $549</t>
+          <t>PLAN RECURRENTE PAGO INCIAL $1,549 HE</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>1549</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>03-03-2026 09:15:14</t>
+          <t>01-03-2026 12:41:08</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>03-03-2026 09:12:40</t>
+          <t>01-03-2026 12:40:23</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1924,36 +1928,36 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>26280522834570008225</t>
+          <t>26280522769240007906</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr"/>
       <c r="Z11" t="inlineStr"/>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>1549</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>Josue Radames Rosales Rojas</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>346743</t>
+          <t>347503</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>88908</t>
+          <t>89668</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1963,17 +1967,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>ENRIQUE</t>
+          <t xml:space="preserve">ENDRID </t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>GUZMAN</t>
+          <t>BELTRAN</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>LARA</t>
+          <t>VAZQUEZ</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1983,12 +1987,12 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>5554577605</t>
+          <t>5565644393</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>TLALPAN</t>
+          <t>INSURGENTES SUR</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1998,17 +2002,17 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>14-03-1976</t>
+          <t>13-07-2005</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>EGUZMANL@GMAIL.COM</t>
+          <t>YAMILEMF8@GMAIL.COM</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>26-02-2026 16:01:03</t>
+          <t>02-03-2026 11:18:02</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -2018,32 +2022,32 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>DOMICILIADO PLAN ULTRA PAGO INCIAL 12 MESES $1,549 HE</t>
+          <t>CONVENIO DOMICILIADO $549</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>1549</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>02-03-2026 16:33:50</t>
+          <t>03-03-2026 11:36:28</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>03-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>02-03-2026 16:32:53</t>
+          <t>03-03-2026 11:33:50</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -2053,7 +2057,7 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
@@ -2063,18 +2067,14 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>26280522801940008093</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS WEB</t>
-        </is>
-      </c>
+          <t>26280522837720008249</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr"/>
       <c r="Z12" t="inlineStr"/>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>1549</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -2091,12 +2091,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>347371</t>
+          <t>346390</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>89536</t>
+          <t>88555</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2106,17 +2106,17 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>ALBERTO</t>
+          <t>LESLIE AIDE</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">ORTIGOZA </t>
+          <t>BIRRICHAGA</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>PEREZ</t>
+          <t>CHAVEZ</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -2126,32 +2126,32 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>5649112537</t>
+          <t>5547192785</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>HERRERIAS</t>
+          <t>TLALPAN</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>14-11-2013</t>
+          <t>25-02-1997</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>ALBERTOOGAZA@GMAIL.COM</t>
+          <t>BIRRICHAGACHAVEZ@GMAIL.COM</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>02-03-2026 04:30:26</t>
+          <t>25-02-2026 08:46:56</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -2161,32 +2161,32 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>CONVENIO DOMICILIADO $549</t>
+          <t>DOMICILIADO 12 MESES $649 HE</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>02-03-2026 04:40:19</t>
+          <t>04-03-2026 10:49:08</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>04-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>02-03-2026 04:39:54</t>
+          <t>04-03-2026 10:48:10</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -2206,14 +2206,14 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>26280522772000007922</t>
+          <t>26280522878970008469</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr"/>
       <c r="Z13" t="inlineStr"/>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -2230,12 +2230,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>347680</t>
+          <t>347367</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>89845</t>
+          <t>89532</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2245,17 +2245,17 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>ARTURO</t>
+          <t>GRISELDA</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>HERNANDEZ</t>
+          <t>ROMERO</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>MAGALLON</t>
+          <t>CASAS</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -2265,28 +2265,32 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>5610667660</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>5541019261</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>CALLEJON DEL FRESNO 8</t>
+        </is>
+      </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>14-11-1975</t>
+          <t>09-01-2001</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>HE.MAGALLON@GMAIL.COM</t>
+          <t>GRISELDAROMERO19429@GMAIL.COM</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>02-03-2026 16:35:10</t>
+          <t>02-03-2026 03:08:05</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -2296,36 +2300,44 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>1 MES $999</t>
+          <t>DOMICILIADO 12 MESES $649 HE</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>999</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>02-03-2026 16:46:28</t>
+          <t>04-03-2026 03:15:54</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T14" t="inlineStr"/>
+          <t>04-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>04-03-2026 03:12:40</t>
+        </is>
+      </c>
       <c r="U14" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V14" t="inlineStr"/>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W14" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2333,36 +2345,40 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>26280522803020008099</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr"/>
+          <t>26280522862800008411</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
       <c r="Z14" t="inlineStr"/>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>999</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Christian Yair Peña Villa</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>347482</t>
+          <t>346388</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>89647</t>
+          <t>88553</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2372,17 +2388,17 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>DAVID</t>
+          <t xml:space="preserve">RAISA ITZEL </t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>LLANOS</t>
+          <t xml:space="preserve">MONTERO </t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>LEGORRETA</t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -2392,32 +2408,32 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>5620518609</t>
+          <t>5528002913</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>PLUTARCO ELIAS CALLES</t>
+          <t>TLALPAN</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>07-04-1974</t>
+          <t>22-02-1988</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>DAVIDLEGORRETA@HOTMAIL.COM</t>
+          <t>RAISAMONTEROMARTINEZ@GMAIL.COM</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>02-03-2026 10:20:10</t>
+          <t>25-02-2026 08:43:52</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -2427,32 +2443,32 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $649 HE</t>
+          <t>PLAN RECURRENTE PAGO INCIAL $1,549 HE</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>1549</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>03-03-2026 04:33:30</t>
+          <t>01-03-2026 12:36:04</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>03-03-2026 04:29:55</t>
+          <t>01-03-2026 12:35:15</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2462,7 +2478,7 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
@@ -2472,14 +2488,14 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>26280522822310008190</t>
+          <t>26280522769120007905</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr"/>
       <c r="Z15" t="inlineStr"/>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>1549</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -2496,12 +2512,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>347565</t>
+          <t>347046</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>89730</t>
+          <t>89211</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2511,17 +2527,17 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>JESUS MIGUEL</t>
+          <t>GIOVANNA</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>FREGOSO</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>VILLEGAS</t>
+          <t>BARRERA</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -2531,32 +2547,28 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2223618726</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>TLALPAN</t>
-        </is>
-      </c>
+          <t>4428692086</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>07-05-1994</t>
+          <t>02-10-2002</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>MIGUEL_LV94@HOTMAIL.COM</t>
+          <t>GIOVANNAFREGOSO269@GMAIL.COM</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>02-03-2026 13:29:01</t>
+          <t>27-02-2026 18:08:30</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -2571,27 +2583,27 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>PLAN RECURRENTE PAGO INCIAL $1,549 HE</t>
+          <t>CONVENIO DOMICILIADO $549</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>1549</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>02-03-2026 13:35:29</t>
+          <t>03-03-2026 18:38:08</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>03-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>02-03-2026 13:34:42</t>
+          <t>03-03-2026 18:37:34</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2601,7 +2613,7 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
@@ -2611,19 +2623,23 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>26280522793220008032</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr"/>
+          <t>26280522855830008380</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
       <c r="Z16" t="inlineStr"/>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>1549</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>Diana Itzel Martinez Colín</t>
+          <t>Christian Yair Peña Villa</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -2635,12 +2651,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>347569</t>
+          <t>347674</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>89734</t>
+          <t>89839</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2650,17 +2666,17 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>YURIDIA</t>
+          <t>ARMANDO</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>ROMAN</t>
+          <t>ARCOS</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>LAUREL</t>
+          <t>MARTINES</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2670,7 +2686,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>7444494140</t>
+          <t>4811008585</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2680,22 +2696,22 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>15-09-1972</t>
+          <t>28-08-1997</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>YURISLIRIS@YAHOO.COM</t>
+          <t>MEDICINAUASLP13@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>02-03-2026 13:33:31</t>
+          <t>02-03-2026 16:28:39</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -2705,32 +2721,32 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>CONVENIO DOMICILIADO $549</t>
+          <t>DOMICILIADO 12 MESES $649 HE</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>02-03-2026 13:42:53</t>
+          <t>02-03-2026 17:40:11</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>03-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>02-03-2026 13:40:35</t>
+          <t>02-03-2026 17:39:26</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2750,14 +2766,22 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>26280522793430008035</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr"/>
-      <c r="Z17" t="inlineStr"/>
+          <t>26280522807450008117</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>Gabriel Pacheco Sanchez</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -2774,12 +2798,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>347674</t>
+          <t>347446</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>89839</t>
+          <t>89611</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2789,17 +2813,17 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>ARMANDO</t>
+          <t>CELIA</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>ARCOS</t>
+          <t xml:space="preserve">RUIZ </t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>MARTINES</t>
+          <t>BAEZ</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2809,32 +2833,28 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>4811008585</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>TLALPAN</t>
-        </is>
-      </c>
+          <t>5534529869</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>28-08-1997</t>
+          <t>03-02-1947</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>MEDICINAUASLP13@HOTMAIL.COM</t>
+          <t>BARUCE03@GMAIL.COM</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>02-03-2026 16:28:39</t>
+          <t>02-03-2026 08:33:45</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2844,44 +2864,36 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $649 HE</t>
+          <t>ANUALIDAD + MES REGALO $6,999</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>538.38</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>02-03-2026 17:40:11</t>
+          <t>02-03-2026 15:13:40</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>02-03-2026 17:39:26</t>
-        </is>
-      </c>
+          <t>02-04-2027 23:59:59</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr"/>
       <c r="U18" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V18" t="inlineStr"/>
       <c r="W18" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2889,22 +2901,14 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>26280522807450008117</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>Gabriel Pacheco Sanchez</t>
-        </is>
-      </c>
+          <t>26280522796960008056</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr"/>
+      <c r="Z18" t="inlineStr"/>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>6999</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -2921,12 +2925,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>347604</t>
+          <t>346743</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>89769</t>
+          <t>88908</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2936,17 +2940,17 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ALEXIS </t>
+          <t>ENRIQUE</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>CABRERA</t>
+          <t>GUZMAN</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>GONZALEZ</t>
+          <t>LARA</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2956,7 +2960,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>5573598515</t>
+          <t>5554577605</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2971,17 +2975,17 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>09-04-2005</t>
+          <t>14-03-1976</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>ALEXBORRE2005@GMAIL.COM</t>
+          <t>EGUZMANL@GMAIL.COM</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>02-03-2026 14:48:34</t>
+          <t>26-02-2026 16:01:03</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -2991,22 +2995,22 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>CONVENIO DOMICILIADO $549</t>
+          <t>DOMICILIADO PLAN ULTRA PAGO INCIAL 12 MESES $1,549 HE</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>1549</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>02-03-2026 17:06:11</t>
+          <t>02-03-2026 16:33:50</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -3016,7 +3020,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>02-03-2026 17:05:43</t>
+          <t>02-03-2026 16:32:53</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -3026,7 +3030,7 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
@@ -3036,36 +3040,40 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>26280522804840008105</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr"/>
+          <t>26280522801940008093</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
       <c r="Z19" t="inlineStr"/>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>1549</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Christian Yair Peña Villa</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>347777</t>
+          <t>347604</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>89942</t>
+          <t>89769</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -3075,17 +3083,17 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>CHRISTIAN IVAN</t>
+          <t xml:space="preserve">ALEXIS </t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>MERUBIA</t>
+          <t>CABRERA</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>NAVIA</t>
+          <t>GONZALEZ</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -3095,7 +3103,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>5611521821</t>
+          <t>5573598515</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -3110,17 +3118,17 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>19-10-1992</t>
+          <t>09-04-2005</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>CHRIS_MERUBIA@HOTMAIL.COM</t>
+          <t>ALEXBORRE2005@GMAIL.COM</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>02-03-2026 17:55:56</t>
+          <t>02-03-2026 14:48:34</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -3130,32 +3138,32 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $649 HE</t>
+          <t>CONVENIO DOMICILIADO $549</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>02-03-2026 19:27:30</t>
+          <t>02-03-2026 17:06:11</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>02-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>02-03-2026 19:26:52</t>
+          <t>02-03-2026 17:05:43</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -3175,18 +3183,14 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>26280522816680008169</t>
-        </is>
-      </c>
-      <c r="Y20" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS WEB</t>
-        </is>
-      </c>
+          <t>26280522804840008105</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr"/>
       <c r="Z20" t="inlineStr"/>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -3203,12 +3207,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>347503</t>
+          <t>347777</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>89668</t>
+          <t>89942</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -3218,17 +3222,17 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">ENDRID </t>
+          <t>CHRISTIAN IVAN</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>BELTRAN</t>
+          <t>MERUBIA</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>VAZQUEZ</t>
+          <t>NAVIA</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -3238,12 +3242,12 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>5565644393</t>
+          <t>5611521821</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>INSURGENTES SUR</t>
+          <t>TLALPAN</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -3253,17 +3257,17 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>13-07-2005</t>
+          <t>19-10-1992</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>YAMILEMF8@GMAIL.COM</t>
+          <t>CHRIS_MERUBIA@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>02-03-2026 11:18:02</t>
+          <t>02-03-2026 17:55:56</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -3273,22 +3277,22 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>CONVENIO DOMICILIADO $549</t>
+          <t>DOMICILIADO 12 MESES $649 HE</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>03-03-2026 11:36:28</t>
+          <t>02-03-2026 19:27:30</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -3298,7 +3302,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>03-03-2026 11:33:50</t>
+          <t>02-03-2026 19:26:52</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -3318,14 +3322,18 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>26280522837720008249</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr"/>
+          <t>26280522816680008169</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
       <c r="Z21" t="inlineStr"/>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -3735,12 +3743,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>347446</t>
+          <t>348179</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>89611</t>
+          <t>90344</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3750,17 +3758,17 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>CELIA</t>
+          <t xml:space="preserve">ANDREA </t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t xml:space="preserve">RUIZ </t>
+          <t xml:space="preserve">NICOLAS </t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>BAEZ</t>
+          <t xml:space="preserve">FLORES </t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -3770,10 +3778,14 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>5534529869</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>5561653454</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>TLALPAN</t>
+        </is>
+      </c>
       <c r="J25" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -3781,17 +3793,17 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>03-02-1947</t>
+          <t>05-04-1999</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>BARUCE03@GMAIL.COM</t>
+          <t>NIFAANDREA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>02-03-2026 08:33:45</t>
+          <t>03-03-2026 17:32:31</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -3801,36 +3813,44 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>ANUALIDAD + MES REGALO $6,999</t>
+          <t>DOMICILIADO PLAN ULTRA PAGO INCIAL 12 MESES $1,549 HE</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>538.38</t>
+          <t>1549</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>02-03-2026 15:13:40</t>
+          <t>03-03-2026 17:42:08</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>02-04-2027 23:59:59</t>
-        </is>
-      </c>
-      <c r="T25" t="inlineStr"/>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>03-03-2026 17:41:31</t>
+        </is>
+      </c>
       <c r="U25" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V25" t="inlineStr"/>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W25" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3838,36 +3858,36 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>26280522796960008056</t>
+          <t>26280522851620008359</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr"/>
       <c r="Z25" t="inlineStr"/>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>6999</t>
+          <t>1549</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Diana Itzel Martinez Colín</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>347685</t>
+          <t>348270</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>89850</t>
+          <t>90435</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3877,17 +3897,17 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NAHOMI</t>
+          <t xml:space="preserve">BRENDA </t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>CABRERA</t>
+          <t xml:space="preserve">VALLE </t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>GONZALEZ</t>
+          <t xml:space="preserve">VILLEGAS </t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -3897,7 +3917,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>5559971564</t>
+          <t>5528942610</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -3912,17 +3932,17 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>29-06-2000</t>
+          <t>16-04-1998</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>NAHOMICABRERAG.29@GMAIL.COM</t>
+          <t>BRE160498V@GMAIL.COM</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>02-03-2026 16:37:42</t>
+          <t>03-03-2026 19:31:08</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -3937,27 +3957,27 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>DOMICILIADO PLAN ULTRA PAGO INCIAL 12 MESES $1,549 HE</t>
+          <t>DOMICILIADO 12 MESES $649 HE</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>1549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>02-03-2026 16:58:55</t>
+          <t>03-03-2026 19:40:05</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>03-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>02-03-2026 16:57:34</t>
+          <t>03-03-2026 19:39:01</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3977,14 +3997,14 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>26280522804160008103</t>
+          <t>26280522859590008403</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr"/>
       <c r="Z26" t="inlineStr"/>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>1549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
@@ -4001,12 +4021,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>347715</t>
+          <t>347685</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>89880</t>
+          <t>89850</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -4016,17 +4036,17 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>EDUARDO LOPEZ</t>
+          <t>NAHOMI</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t xml:space="preserve">LOPEZ </t>
+          <t>CABRERA</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t xml:space="preserve">SANTANA </t>
+          <t>GONZALEZ</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -4036,32 +4056,32 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>5530598571</t>
+          <t>5559971564</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t xml:space="preserve">TLALPAN </t>
+          <t>TLALPAN</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>04-01-2001</t>
+          <t>29-06-2000</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>EDUARDOLOPEZSANTANA1A@GMAIL.COM</t>
+          <t>NAHOMICABRERAG.29@GMAIL.COM</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>02-03-2026 17:02:13</t>
+          <t>02-03-2026 16:37:42</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -4071,22 +4091,22 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>RECURRENTE $799 HE</t>
+          <t>DOMICILIADO PLAN ULTRA PAGO INCIAL 12 MESES $1,549 HE</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>1549</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>02-03-2026 17:14:28</t>
+          <t>02-03-2026 16:58:55</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -4096,7 +4116,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>02-03-2026 17:09:16</t>
+          <t>02-03-2026 16:57:34</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -4116,36 +4136,36 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>26280522805500008106</t>
+          <t>26280522804160008103</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr"/>
       <c r="Z27" t="inlineStr"/>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>1549</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Christian Yair Peña Villa</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>348081</t>
+          <t>347715</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>90246</t>
+          <t>89880</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -4155,17 +4175,17 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">NATALIA </t>
+          <t>EDUARDO LOPEZ</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t xml:space="preserve">SANCHEZ </t>
+          <t xml:space="preserve">LOPEZ </t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>MENDOZA</t>
+          <t xml:space="preserve">SANTANA </t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -4175,32 +4195,32 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>5545290873</t>
+          <t>5530598571</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>TLALPAN</t>
+          <t xml:space="preserve">TLALPAN </t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>29-08-2007</t>
+          <t>04-01-2001</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>NATALIAMENDOZA790101@GMAIL.COM</t>
+          <t>EDUARDOLOPEZSANTANA1A@GMAIL.COM</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>03-03-2026 15:19:31</t>
+          <t>02-03-2026 17:02:13</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -4210,32 +4230,32 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>DOMICILIADO PLAN ULTRA PAGO INCIAL 12 MESES $1,549 HE</t>
+          <t>RECURRENTE $799 HE</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>1549</t>
+          <t>799</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>03-03-2026 15:29:19</t>
+          <t>02-03-2026 17:14:28</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>02-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>03-03-2026 15:28:33</t>
+          <t>02-03-2026 17:09:16</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -4245,7 +4265,7 @@
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W28" t="inlineStr">
@@ -4255,14 +4275,14 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>26280522843920008315</t>
+          <t>26280522805500008106</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr"/>
       <c r="Z28" t="inlineStr"/>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>1549</t>
+          <t>799</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
@@ -4279,12 +4299,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>348134</t>
+          <t>347566</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>90299</t>
+          <t>89731</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -4294,17 +4314,17 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>PABLO ANGEL</t>
+          <t>ERIC</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t xml:space="preserve">CARRILLO </t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>JUAREZ</t>
+          <t>ROMAN</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -4314,10 +4334,14 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>5544502085</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>5540969149</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>TLALPAN</t>
+        </is>
+      </c>
       <c r="J29" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -4325,17 +4349,17 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>12-10-1998</t>
+          <t>08-08-2008</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>PABLOACARRILLOJ@GMAIL.COM</t>
+          <t>ERICSAN08@GMAIL.COM</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>03-03-2026 16:49:36</t>
+          <t>02-03-2026 13:30:16</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -4345,12 +4369,12 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>CONVENIO DOMICILIADO $549</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
@@ -4360,21 +4384,29 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>03-03-2026 16:58:26</t>
+          <t>02-03-2026 13:48:48</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T29" t="inlineStr"/>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>02-03-2026 13:45:33</t>
+        </is>
+      </c>
       <c r="U29" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V29" t="inlineStr"/>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W29" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4382,7 +4414,7 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>26280522848750008333</t>
+          <t>26280522793620008038</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr"/>
@@ -4406,12 +4438,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>348207</t>
+          <t>348189</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>90372</t>
+          <t>90354</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -4421,17 +4453,17 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>YESELMI EMELIN</t>
+          <t xml:space="preserve">MATEO </t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRIVIESCA </t>
+          <t xml:space="preserve">SUAREZ </t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t xml:space="preserve">MEJIA </t>
+          <t xml:space="preserve">PICHARDO </t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -4441,28 +4473,28 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>5581061114</t>
+          <t>5633352915</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>27-08-2007</t>
+          <t>02-12-2010</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>BRIVIESCAYUSLEMI@GMAIL.COM</t>
+          <t>MATEO.SUAREZ0212@GMAIL.COM</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>03-03-2026 18:00:26</t>
+          <t>03-03-2026 17:44:32</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -4487,7 +4519,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>03-03-2026 18:19:14</t>
+          <t>03-03-2026 18:00:56</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
@@ -4497,7 +4529,7 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>03-03-2026 18:18:38</t>
+          <t>03-03-2026 18:00:15</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -4507,7 +4539,7 @@
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W30" t="inlineStr">
@@ -4517,7 +4549,7 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>26280522854400008370</t>
+          <t>26280522853110008366</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr"/>
@@ -4541,12 +4573,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>348009</t>
+          <t>348350</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>90174</t>
+          <t>90515</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -4556,17 +4588,17 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">KEVIN </t>
+          <t>ISMAEL</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>OSORIA</t>
+          <t>DIAZ</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>CORTINAS</t>
+          <t>GONZALEZ</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -4576,10 +4608,14 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>8662568650</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>5585277569</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>QUECHOLE</t>
+        </is>
+      </c>
       <c r="J31" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -4587,17 +4623,17 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>11-01-2003</t>
+          <t>23-10-2010</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>KEVINOSORIA57@GMAIL.COM</t>
+          <t>PEDROALCARON9@GMAIL.COM</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>03-03-2026 11:14:35</t>
+          <t>04-03-2026 08:20:20</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -4607,12 +4643,12 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>CONVENIO DOMICILIADO $549</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
@@ -4622,21 +4658,29 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>03-03-2026 11:30:05</t>
+          <t>04-03-2026 08:34:17</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T31" t="inlineStr"/>
+          <t>04-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>04-03-2026 08:33:45</t>
+        </is>
+      </c>
       <c r="U31" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V31" t="inlineStr"/>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W31" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4644,7 +4688,7 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>26280522837550008246</t>
+          <t>26280522876130008449</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr"/>
@@ -4656,24 +4700,24 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>Diana Itzel Martinez Colín</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>348141</t>
+          <t>348071</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>90306</t>
+          <t>90236</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -4683,17 +4727,17 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>BERTHA MARIA</t>
+          <t>MIGUEL ANGEL</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t xml:space="preserve">BALDERAS </t>
+          <t xml:space="preserve">FUENTES </t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>ARENAS</t>
+          <t>AVILA</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -4703,28 +4747,32 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>5554577198</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>3339470808</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>TLALPAN</t>
+        </is>
+      </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>17-01-1971</t>
+          <t>29-09-1982</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>BERTHACAMPERO@YAHOO.COM</t>
+          <t>FUENTESAVILA82@YAHOO.COM.MX</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>03-03-2026 17:00:25</t>
+          <t>03-03-2026 14:58:35</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -4734,22 +4782,22 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $649 HE</t>
+          <t>RECURRENTE $799 HE</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>799</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>03-03-2026 17:10:00</t>
+          <t>03-03-2026 15:07:01</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
@@ -4759,7 +4807,7 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>03-03-2026 17:09:07</t>
+          <t>03-03-2026 15:06:31</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -4769,7 +4817,7 @@
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W32" t="inlineStr">
@@ -4779,36 +4827,36 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>26280522849360008343</t>
+          <t>26280522843090008308</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr"/>
       <c r="Z32" t="inlineStr"/>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>799</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>Omar Carillo Leal</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>348179</t>
+          <t>347929</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>90344</t>
+          <t>90094</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -4818,17 +4866,17 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">ANDREA </t>
+          <t>FRANK</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t xml:space="preserve">NICOLAS </t>
+          <t>VIGUERAS</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t xml:space="preserve">FLORES </t>
+          <t>HERNÁNDEZ</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -4838,32 +4886,28 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>5561653454</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>TLALPAN</t>
-        </is>
-      </c>
+          <t>7712142767</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>05-04-1999</t>
+          <t>17-05-1992</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>NIFAANDREA@GMAIL.COM</t>
+          <t>VIGUERASFRANK06@GMAIL.COM</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>03-03-2026 17:32:31</t>
+          <t>03-03-2026 04:45:32</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -4873,44 +4917,36 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>DOMICILIADO PLAN ULTRA PAGO INCIAL 12 MESES $1,549 HE</t>
+          <t>3 MESES $2,099</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>1549</t>
+          <t>699.67</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>03-03-2026 17:42:08</t>
+          <t>05-03-2026 08:24:41</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>03-03-2026 17:41:31</t>
-        </is>
-      </c>
+          <t>05-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr"/>
       <c r="U33" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V33" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="V33" t="inlineStr"/>
       <c r="W33" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4918,14 +4954,18 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>26280522851620008359</t>
-        </is>
-      </c>
-      <c r="Y33" t="inlineStr"/>
+          <t>26280522910670008656</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
       <c r="Z33" t="inlineStr"/>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>1549</t>
+          <t>2099</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
@@ -4942,12 +4982,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>348273</t>
+          <t>347759</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>90438</t>
+          <t>89924</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -4957,17 +4997,17 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">JERONIMO </t>
+          <t>CARLOS</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t xml:space="preserve">SOTO </t>
+          <t xml:space="preserve">MARTINEZ </t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t xml:space="preserve">ORTEGA </t>
+          <t>ZARZA</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -4977,7 +5017,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>5567035457</t>
+          <t>5517473620</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -4992,17 +5032,17 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>12-10-1992</t>
+          <t>24-03-1984</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>MOMO851245@GMAIL.COM</t>
+          <t>EMZARZA4@GMAIL.COM</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>03-03-2026 19:34:21</t>
+          <t>02-03-2026 17:40:33</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -5017,27 +5057,27 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $649 HE</t>
+          <t>DOMICILIADO PLAN ULTRA PAGO INCIAL 12 MESES $1,549 HE</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>1549</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>03-03-2026 19:43:09</t>
+          <t>02-03-2026 17:52:53</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>02-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>03-03-2026 19:42:28</t>
+          <t>02-03-2026 17:52:23</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -5047,7 +5087,7 @@
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W34" t="inlineStr">
@@ -5057,14 +5097,14 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>26280522859660008404</t>
+          <t>26280522808850008128</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr"/>
       <c r="Z34" t="inlineStr"/>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>1549</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
@@ -5081,12 +5121,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>348270</t>
+          <t>347981</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>90435</t>
+          <t>90146</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -5096,17 +5136,17 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRENDA </t>
+          <t xml:space="preserve">VALERIA </t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t xml:space="preserve">VALLE </t>
+          <t>RUIZ</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t xml:space="preserve">VILLEGAS </t>
+          <t>MACIAS</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -5116,12 +5156,12 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>5528942610</t>
+          <t>5571120475</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>TLALPAN</t>
+          <t>COL SAN JUAN DE ARAGON</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -5131,17 +5171,17 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>16-04-1998</t>
+          <t>16-07-2004</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>BRE160498V@GMAIL.COM</t>
+          <t>VALERIA.A.RUIZ@OUTLOOK.COM</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>03-03-2026 19:31:08</t>
+          <t>03-03-2026 09:02:04</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -5151,22 +5191,22 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $649 HE</t>
+          <t>CONVENIO DOMICILIADO $549</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>03-03-2026 19:40:05</t>
+          <t>03-03-2026 09:15:14</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
@@ -5176,7 +5216,7 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>03-03-2026 19:39:01</t>
+          <t>03-03-2026 09:12:40</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -5186,7 +5226,7 @@
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W35" t="inlineStr">
@@ -5196,36 +5236,36 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>26280522859590008403</t>
+          <t>26280522834570008225</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr"/>
       <c r="Z35" t="inlineStr"/>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Josue Radames Rosales Rojas</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>347566</t>
+          <t>347033</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>89731</t>
+          <t>89198</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -5235,17 +5275,17 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>ERIC</t>
+          <t xml:space="preserve">VALERIA ALEJANDRA </t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t xml:space="preserve">PADILLA </t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>ROMAN</t>
+          <t xml:space="preserve">CASE </t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -5255,7 +5295,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>5540969149</t>
+          <t>5512118910</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -5265,22 +5305,22 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>08-08-2008</t>
+          <t>03-02-2006</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>ERICSAN08@GMAIL.COM</t>
+          <t>VALERIACASEPER@GMAIL.COM</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>02-03-2026 13:30:16</t>
+          <t>27-02-2026 17:40:59</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -5305,17 +5345,17 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>02-03-2026 13:48:48</t>
+          <t>01-03-2026 13:25:12</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>02-03-2026 13:45:33</t>
+          <t>01-03-2026 13:23:47</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -5335,7 +5375,7 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>26280522793620008038</t>
+          <t>26280522769860007910</t>
         </is>
       </c>
       <c r="Y36" t="inlineStr"/>
@@ -5359,12 +5399,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>348189</t>
+          <t>347371</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>90354</t>
+          <t>89536</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -5374,17 +5414,17 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">MATEO </t>
+          <t>ALBERTO</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t xml:space="preserve">SUAREZ </t>
+          <t xml:space="preserve">ORTIGOZA </t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t xml:space="preserve">PICHARDO </t>
+          <t>PEREZ</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -5394,10 +5434,14 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>5633352915</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>5649112537</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>HERRERIAS</t>
+        </is>
+      </c>
       <c r="J37" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -5405,17 +5449,17 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>02-12-2010</t>
+          <t>14-11-2013</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>MATEO.SUAREZ0212@GMAIL.COM</t>
+          <t>ALBERTOOGAZA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>03-03-2026 17:44:32</t>
+          <t>02-03-2026 04:30:26</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -5440,17 +5484,17 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>03-03-2026 18:00:56</t>
+          <t>02-03-2026 04:40:19</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>02-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>03-03-2026 18:00:15</t>
+          <t>02-03-2026 04:39:54</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
@@ -5460,7 +5504,7 @@
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W37" t="inlineStr">
@@ -5470,7 +5514,7 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>26280522853110008366</t>
+          <t>26280522772000007922</t>
         </is>
       </c>
       <c r="Y37" t="inlineStr"/>
@@ -5494,12 +5538,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>348071</t>
+          <t>348490</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>90236</t>
+          <t>90655</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -5509,17 +5553,17 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>MIGUEL ANGEL</t>
+          <t xml:space="preserve">JESUS </t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t xml:space="preserve">FUENTES </t>
+          <t xml:space="preserve">QUINTANA </t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>AVILA</t>
+          <t xml:space="preserve">ANDRADE </t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -5529,7 +5573,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>3339470808</t>
+          <t>6141674674</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -5544,17 +5588,17 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>29-09-1982</t>
+          <t>10-03-1999</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>FUENTESAVILA82@YAHOO.COM.MX</t>
+          <t>CHUYIN711@GMAIL.COM</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>03-03-2026 14:58:35</t>
+          <t>04-03-2026 16:45:26</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -5564,32 +5608,32 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>RECURRENTE $799 HE</t>
+          <t>DOMICILIADO PLAN ULTRA PAGO INCIAL 12 MESES $1,549 HE</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>1549</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>03-03-2026 15:07:01</t>
+          <t>04-03-2026 16:53:38</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>04-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>03-03-2026 15:06:31</t>
+          <t>04-03-2026 16:52:23</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
@@ -5609,14 +5653,14 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>26280522843090008308</t>
+          <t>26280522888490008569</t>
         </is>
       </c>
       <c r="Y38" t="inlineStr"/>
       <c r="Z38" t="inlineStr"/>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>1549</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
@@ -5633,12 +5677,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>348119</t>
+          <t>348512</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>90284</t>
+          <t>90677</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -5648,17 +5692,17 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">LUIS ARMANDO </t>
+          <t>CARLOS ALEXIS</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t xml:space="preserve">VILLA </t>
+          <t>JUAREZ</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t xml:space="preserve">CHAVEZ </t>
+          <t>DAVILA</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -5668,10 +5712,14 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>6143811757</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>5624037947</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>TLALPAN</t>
+        </is>
+      </c>
       <c r="J39" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -5679,17 +5727,17 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>14-06-1995</t>
+          <t>07-05-2004</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>LUISARMANDOVILLAA@GMAIL.COM</t>
+          <t>CARLOSALEXISMESSI@GMAIL.COM</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>03-03-2026 16:29:37</t>
+          <t>04-03-2026 17:14:37</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -5699,32 +5747,32 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $649 HE</t>
+          <t>CONVENIO DOMICILIADO $549</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>03-03-2026 16:39:07</t>
+          <t>04-03-2026 17:24:16</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>04-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>03-03-2026 16:38:32</t>
+          <t>04-03-2026 17:22:45</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -5734,7 +5782,7 @@
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W39" t="inlineStr">
@@ -5744,22 +5792,1781 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>26280522847410008326</t>
+          <t>26280522890380008587</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr"/>
       <c r="Z39" t="inlineStr"/>
       <c r="AA39" t="inlineStr">
         <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>Carlos Arturo Flores Alvarez</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>348009</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>90174</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>INSURGENTES</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">KEVIN </t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>OSORIA</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>CORTINAS</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>8662568650</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>11-01-2003</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>KEVINOSORIA57@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>03-03-2026 11:14:35</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 HE</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>03-03-2026 11:30:05</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr"/>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr"/>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>26280522837550008246</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr"/>
+      <c r="Z40" t="inlineStr"/>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>Diana Itzel Martinez Colín</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>348141</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>90306</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>INSURGENTES</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>BERTHA MARIA</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BALDERAS </t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>ARENAS</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>5554577198</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>17-01-1971</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>BERTHACAMPERO@YAHOO.COM</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>03-03-2026 17:00:25</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 HE</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $649 HE</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
           <t>649</t>
         </is>
       </c>
-      <c r="AB39" t="inlineStr">
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>03-03-2026 17:10:00</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>03-03-2026 17:09:07</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>26280522849360008343</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr"/>
+      <c r="Z41" t="inlineStr"/>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>Omar Carillo Leal</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>348119</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>90284</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>INSURGENTES</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LUIS ARMANDO </t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VILLA </t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CHAVEZ </t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>6143811757</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>14-06-1995</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>LUISARMANDOVILLAA@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>03-03-2026 16:29:37</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 HE</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $649 HE</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>03-03-2026 16:39:07</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>03-03-2026 16:38:32</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>26280522847410008326</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr"/>
+      <c r="Z42" t="inlineStr"/>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
         <is>
           <t>Christian Yair Peña Villa</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>347680</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>89845</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>INSURGENTES</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>ARTURO</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>MAGALLON</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>5610667660</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>14-11-1975</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>HE.MAGALLON@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>02-03-2026 16:35:10</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 HE</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>1 MES $999</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>02-03-2026 16:46:28</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr"/>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr"/>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>26280522803020008099</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr"/>
+      <c r="Z43" t="inlineStr"/>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>348346</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>90511</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>INSURGENTES</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>JOSUE ABRAHAM</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>DIAZ</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>GONZALEZ</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>5562030737</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>QUECHOLOC</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>01-09-2006</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>RAY23DIAZ23@GMMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>04-03-2026 08:18:28</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 HE</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>CONVENIO DOMICILIADO $549</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>04-03-2026 08:33:04</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>04-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>04-03-2026 08:27:56</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>26280522876040008448</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr"/>
+      <c r="Z44" t="inlineStr"/>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>348384</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>90549</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>INSURGENTES</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CAROLINA </t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>RIVERA</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>NIETO</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>5548650084</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>JOJUTLA</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>10-02-1989</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>CARIV1@LIVE.COM.MX</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>04-03-2026 10:42:15</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 HE</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $649 HE</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>04-03-2026 11:08:00</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>04-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>04-03-2026 10:55:20</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>26280522879210008471</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr"/>
+      <c r="Z45" t="inlineStr"/>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>348081</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>90246</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>INSURGENTES</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NATALIA </t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SANCHEZ </t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>MENDOZA</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>5545290873</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>TLALPAN</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>29-08-2007</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>NATALIAMENDOZA790101@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>03-03-2026 15:19:31</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 HE</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>DOMICILIADO PLAN ULTRA PAGO INCIAL 12 MESES $1,549 HE</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>1549</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>03-03-2026 15:29:19</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>03-03-2026 15:28:33</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>26280522843920008315</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr"/>
+      <c r="Z46" t="inlineStr"/>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>1549</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>348134</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>90299</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>INSURGENTES</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>PABLO ANGEL</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CARRILLO </t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>JUAREZ</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>5544502085</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>12-10-1998</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>PABLOACARRILLOJ@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>03-03-2026 16:49:36</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 HE</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>03-03-2026 16:58:26</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr"/>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr"/>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>26280522848750008333</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr"/>
+      <c r="Z47" t="inlineStr"/>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>348207</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>90372</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>INSURGENTES</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>YESELMI EMELIN</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BRIVIESCA </t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MEJIA </t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>5581061114</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>27-08-2007</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>BRIVIESCAYUSLEMI@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>03-03-2026 18:00:26</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 HE</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>CONVENIO DOMICILIADO $549</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>03-03-2026 18:19:14</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>03-03-2026 18:18:38</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>26280522854400008370</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr"/>
+      <c r="Z48" t="inlineStr"/>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>Diana Itzel Martinez Colín</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>348273</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>90438</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>INSURGENTES</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JERONIMO </t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SOTO </t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ORTEGA </t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>5567035457</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>TLALPAN</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>12-10-1992</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>MOMO851245@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>03-03-2026 19:34:21</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 HE</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $649 HE</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>03-03-2026 19:43:09</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>03-03-2026 19:42:28</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>26280522859660008404</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr"/>
+      <c r="Z49" t="inlineStr"/>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>348470</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>90635</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>INSURGENTES</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AYLEN GUADALUPE </t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SALAZAR </t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RAMIREZ </t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>7446933556</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TLALPAN </t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>26-08-2002</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>SALAZARAYLEN0@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>04-03-2026 15:51:49</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 HE</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $649 HE</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>04-03-2026 16:06:18</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>04-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>04-03-2026 15:58:52</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>26280522886430008547</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr"/>
+      <c r="Z50" t="inlineStr"/>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>Christian Yair Peña Villa</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>348731</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>90896</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>INSURGENTES</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RAUL </t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>FERREYRA</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>ARCOS</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>4432655416</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>TLALPAN</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>02-03-1999</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>FERRAUL43@HOTMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>05-03-2026 15:40:08</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 HE</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>DOMICILIADO PLAN ULTRA PAGO INCIAL 12 MESES $1,549 HE</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>1549</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>05-03-2026 15:48:47</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>05-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>05-03-2026 15:46:26</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>26280522919580008735</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr"/>
+      <c r="Z51" t="inlineStr"/>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>1549</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>348734</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>90899</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>INSURGENTES</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ELIZABETH </t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>ALCALA</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>SANJUANICO</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>5535537354</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>TLALPAN</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>08-01-1968</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>GOR_A@TELMEXMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>05-03-2026 15:48:40</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 HE</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>DOMICILIADO PLAN ULTRA PAGO INCIAL 12 MESES $1,549 HE</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>1549</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>05-03-2026 16:08:36</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>05-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>05-03-2026 16:05:43</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>26280522920380008738</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr"/>
+      <c r="Z52" t="inlineStr"/>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>1549</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>Christian Yair Peña Villa</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
         <is>
           <t>con rutina</t>
         </is>

--- a/data/rutinas/sucursales/Socios_con_y_sin_rutina__INSURGENTES.xlsx
+++ b/data/rutinas/sucursales/Socios_con_y_sin_rutina__INSURGENTES.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC52"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,12 +578,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>347322</t>
+          <t>344383</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>89487</t>
+          <t>22200</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -593,17 +593,17 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">OSCAR DANIEL </t>
+          <t>YADIRA</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">HERNANDEZ </t>
+          <t>CORREA</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>CARRIZOSA</t>
+          <t>VILLEGAS</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -613,10 +613,14 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2217188025</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>5523151261</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>C CORREGIDORA</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -624,17 +628,17 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>13-02-1997</t>
+          <t>13-06-1977</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>OSHESIER77@GMAIL.COM</t>
+          <t>YCORREA@YAHOO.COM</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>01-03-2026 11:37:19</t>
+          <t>17-02-2026 06:42:07</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -644,32 +648,32 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $649 HE</t>
+          <t>CONVENIO DOMICILIADO $549</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>01-03-2026 11:46:48</t>
+          <t>04-03-2026 04:56:30</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>01-04-2026 23:59:59</t>
+          <t>03-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>01-03-2026 11:46:09</t>
+          <t>04-03-2026 04:53:54</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -679,7 +683,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -689,36 +693,40 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>26280522768240007896</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr"/>
+          <t>26280522864040008421</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
       <c r="Z2" t="inlineStr"/>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>Josue Radames Rosales Rojas</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>347164</t>
+          <t>346390</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>89329</t>
+          <t>88555</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -728,17 +736,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>ALMA LIZET</t>
+          <t>LESLIE AIDE</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>LUNA</t>
+          <t>BIRRICHAGA</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>ARENAS</t>
+          <t>CHAVEZ</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -748,7 +756,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>5561052467</t>
+          <t>5547192785</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -763,17 +771,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>14-10-1975</t>
+          <t>25-02-1997</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>ALMAARENAS777@GMAIL.COM</t>
+          <t>BIRRICHAGACHAVEZ@GMAIL.COM</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>28-02-2026 09:37:15</t>
+          <t>25-02-2026 08:46:56</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -788,17 +796,17 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>DOMICILIADO PLAN ULTRA PAGO INCIAL 12 MESES $1,549 HE</t>
+          <t>DOMICILIADO 12 MESES $649 HE</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>1549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>03-03-2026 14:29:23</t>
+          <t>04-03-2026 10:49:08</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -808,7 +816,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>03-03-2026 14:28:32</t>
+          <t>04-03-2026 10:48:10</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -828,18 +836,14 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>26280522841740008298</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS WEB</t>
-        </is>
-      </c>
+          <t>26280522878970008469</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>1549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -946,7 +950,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
+          <t>09-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1081,7 +1085,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T5" t="inlineStr"/>
@@ -1126,12 +1130,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>344383</t>
+          <t>347033</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>22200</t>
+          <t>89198</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1141,17 +1145,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>YADIRA</t>
+          <t xml:space="preserve">VALERIA ALEJANDRA </t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>CORREA</t>
+          <t xml:space="preserve">PADILLA </t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>VILLEGAS</t>
+          <t xml:space="preserve">CASE </t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1161,32 +1165,32 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>5523151261</t>
+          <t>5512118910</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>C CORREGIDORA</t>
+          <t>TLALPAN</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>13-06-1977</t>
+          <t>03-02-2006</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>YCORREA@YAHOO.COM</t>
+          <t>VALERIACASEPER@GMAIL.COM</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>17-02-2026 06:42:07</t>
+          <t>27-02-2026 17:40:59</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1211,17 +1215,17 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>04-03-2026 04:56:30</t>
+          <t>01-03-2026 13:25:12</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>04-04-2026 23:59:59</t>
+          <t>31-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>04-03-2026 04:53:54</t>
+          <t>01-03-2026 13:23:47</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1231,7 +1235,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1241,14 +1245,10 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>26280522864040008421</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS WEB</t>
-        </is>
-      </c>
+          <t>26280522769860007910</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr"/>
       <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="inlineStr">
         <is>
@@ -1269,12 +1269,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>347482</t>
+          <t>347371</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>89647</t>
+          <t>89536</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1284,17 +1284,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>DAVID</t>
+          <t>ALBERTO</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>LLANOS</t>
+          <t xml:space="preserve">ORTIGOZA </t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>LEGORRETA</t>
+          <t>PEREZ</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1304,12 +1304,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>5620518609</t>
+          <t>5649112537</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>PLUTARCO ELIAS CALLES</t>
+          <t>HERRERIAS</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1319,17 +1319,17 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>07-04-1974</t>
+          <t>14-11-2013</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>DAVIDLEGORRETA@HOTMAIL.COM</t>
+          <t>ALBERTOOGAZA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>02-03-2026 10:20:10</t>
+          <t>02-03-2026 04:30:26</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1339,32 +1339,32 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $649 HE</t>
+          <t>CONVENIO DOMICILIADO $549</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>03-03-2026 04:33:30</t>
+          <t>02-03-2026 04:40:19</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>03-03-2026 04:29:55</t>
+          <t>02-03-2026 04:39:54</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1384,14 +1384,14 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>26280522822310008190</t>
+          <t>26280522772000007922</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr"/>
       <c r="Z7" t="inlineStr"/>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -1408,12 +1408,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>347565</t>
+          <t>347367</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>89730</t>
+          <t>89532</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>JESUS MIGUEL</t>
+          <t>GRISELDA</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>ROMERO</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>VILLEGAS</t>
+          <t>CASAS</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1443,32 +1443,32 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2223618726</t>
+          <t>5541019261</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>TLALPAN</t>
+          <t>CALLEJON DEL FRESNO 8</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>07-05-1994</t>
+          <t>09-01-2001</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>MIGUEL_LV94@HOTMAIL.COM</t>
+          <t>GRISELDAROMERO19429@GMAIL.COM</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>02-03-2026 13:29:01</t>
+          <t>02-03-2026 03:08:05</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1478,32 +1478,32 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>PLAN RECURRENTE PAGO INCIAL $1,549 HE</t>
+          <t>DOMICILIADO 12 MESES $649 HE</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>1549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>02-03-2026 13:35:29</t>
+          <t>04-03-2026 03:15:54</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>03-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>02-03-2026 13:34:42</t>
+          <t>04-03-2026 03:12:40</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
@@ -1523,19 +1523,23 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>26280522793220008032</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr"/>
+          <t>26280522862800008411</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
       <c r="Z8" t="inlineStr"/>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>1549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>Diana Itzel Martinez Colín</t>
+          <t>Christian Yair Peña Villa</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1547,12 +1551,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>347569</t>
+          <t>347283</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>89734</t>
+          <t>89448</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1562,17 +1566,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>YURIDIA</t>
+          <t xml:space="preserve">AXEL ANTONIO </t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>ROMAN</t>
+          <t xml:space="preserve">HERRERA </t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>LAUREL</t>
+          <t xml:space="preserve">RUIZ </t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1582,14 +1586,10 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>7444494140</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>TLALPAN</t>
-        </is>
-      </c>
+          <t>8332617094</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -1597,17 +1597,17 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>15-09-1972</t>
+          <t>26-12-1997</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>YURISLIRIS@YAHOO.COM</t>
+          <t>AXELHERREARUIZ@GMAIL.COM</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>02-03-2026 13:33:31</t>
+          <t>01-03-2026 09:27:23</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1617,44 +1617,36 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>CONVENIO DOMICILIADO $549</t>
+          <t>1 MES $999</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>999</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>02-03-2026 13:42:53</t>
+          <t>01-03-2026 09:32:48</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>02-03-2026 13:40:35</t>
-        </is>
-      </c>
+          <t>31-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr"/>
       <c r="U9" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V9" t="inlineStr"/>
       <c r="W9" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1662,14 +1654,14 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>26280522793430008035</t>
+          <t>26280522765690007884</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr"/>
       <c r="Z9" t="inlineStr"/>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>999</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -1686,12 +1678,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>347283</t>
+          <t>347338</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>89448</t>
+          <t>89503</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1701,17 +1693,17 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">AXEL ANTONIO </t>
+          <t xml:space="preserve">JAIR JOCSAN </t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">HERRERA </t>
+          <t>YBARRA</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t xml:space="preserve">RUIZ </t>
+          <t xml:space="preserve">CORTES </t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1721,28 +1713,32 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>8332617094</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>5971145759</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>TLALPAN</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>26-12-1997</t>
+          <t>24-06-1996</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>AXELHERREARUIZ@GMAIL.COM</t>
+          <t>JAIRIBACOR@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>01-03-2026 09:27:23</t>
+          <t>01-03-2026 12:27:06</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1752,36 +1748,44 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>1 MES $999</t>
+          <t>PLAN RECURRENTE PAGO INCIAL $1,549 HE</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>999</t>
+          <t>1549</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>01-03-2026 09:32:48</t>
+          <t>01-03-2026 12:41:08</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>01-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr"/>
+          <t>31-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>01-03-2026 12:40:23</t>
+        </is>
+      </c>
       <c r="U10" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr"/>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W10" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1789,14 +1793,14 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>26280522765690007884</t>
+          <t>26280522769240007906</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr"/>
       <c r="Z10" t="inlineStr"/>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>999</t>
+          <t>1549</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -1813,12 +1817,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>347338</t>
+          <t>347503</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>89503</t>
+          <t>89668</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1828,17 +1832,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">JAIR JOCSAN </t>
+          <t xml:space="preserve">ENDRID </t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>YBARRA</t>
+          <t>BELTRAN</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t xml:space="preserve">CORTES </t>
+          <t>VAZQUEZ</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1848,12 +1852,12 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>5971145759</t>
+          <t>5565644393</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>TLALPAN</t>
+          <t>INSURGENTES SUR</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1863,17 +1867,17 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>24-06-1996</t>
+          <t>13-07-2005</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>JAIRIBACOR@HOTMAIL.COM</t>
+          <t>YAMILEMF8@GMAIL.COM</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>01-03-2026 12:27:06</t>
+          <t>02-03-2026 11:18:02</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1888,27 +1892,27 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>PLAN RECURRENTE PAGO INCIAL $1,549 HE</t>
+          <t>CONVENIO DOMICILIADO $549</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>1549</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>01-03-2026 12:41:08</t>
+          <t>03-03-2026 11:36:28</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>01-04-2026 23:59:59</t>
+          <t>02-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>01-03-2026 12:40:23</t>
+          <t>03-03-2026 11:33:50</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1918,7 +1922,7 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
@@ -1928,14 +1932,14 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>26280522769240007906</t>
+          <t>26280522837720008249</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr"/>
       <c r="Z11" t="inlineStr"/>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>1549</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -1952,12 +1956,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>347503</t>
+          <t>347446</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>89668</t>
+          <t>89611</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1967,17 +1971,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">ENDRID </t>
+          <t>CELIA</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>BELTRAN</t>
+          <t xml:space="preserve">RUIZ </t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>VAZQUEZ</t>
+          <t>BAEZ</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1987,32 +1991,28 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>5565644393</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>INSURGENTES SUR</t>
-        </is>
-      </c>
+          <t>5534529869</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>13-07-2005</t>
+          <t>03-02-1947</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>YAMILEMF8@GMAIL.COM</t>
+          <t>BARUCE03@GMAIL.COM</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>02-03-2026 11:18:02</t>
+          <t>02-03-2026 08:33:45</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -2022,44 +2022,36 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>CONVENIO DOMICILIADO $549</t>
+          <t>ANUALIDAD + MES REGALO $6,999</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>538.38</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>03-03-2026 11:36:28</t>
+          <t>02-03-2026 15:13:40</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>03-03-2026 11:33:50</t>
-        </is>
-      </c>
+          <t>01-04-2027 23:59:59</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr"/>
       <c r="U12" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V12" t="inlineStr"/>
       <c r="W12" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2067,14 +2059,14 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>26280522837720008249</t>
+          <t>26280522796960008056</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr"/>
       <c r="Z12" t="inlineStr"/>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>6999</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -2091,12 +2083,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>346390</t>
+          <t>346743</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>88555</t>
+          <t>88908</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2106,17 +2098,17 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LESLIE AIDE</t>
+          <t>ENRIQUE</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>BIRRICHAGA</t>
+          <t>GUZMAN</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CHAVEZ</t>
+          <t>LARA</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -2126,7 +2118,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>5547192785</t>
+          <t>5554577605</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -2136,22 +2128,22 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>25-02-1997</t>
+          <t>14-03-1976</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>BIRRICHAGACHAVEZ@GMAIL.COM</t>
+          <t>EGUZMANL@GMAIL.COM</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>25-02-2026 08:46:56</t>
+          <t>26-02-2026 16:01:03</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -2166,27 +2158,27 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $649 HE</t>
+          <t>DOMICILIADO PLAN ULTRA PAGO INCIAL 12 MESES $1,549 HE</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>1549</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>04-03-2026 10:49:08</t>
+          <t>02-03-2026 16:33:50</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>04-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>04-03-2026 10:48:10</t>
+          <t>02-03-2026 16:32:53</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -2196,7 +2188,7 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
@@ -2206,36 +2198,40 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>26280522878970008469</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr"/>
+          <t>26280522801940008093</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
       <c r="Z13" t="inlineStr"/>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>1549</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Christian Yair Peña Villa</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>347367</t>
+          <t>347322</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>89532</t>
+          <t>89487</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2245,17 +2241,17 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>GRISELDA</t>
+          <t xml:space="preserve">OSCAR DANIEL </t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>ROMERO</t>
+          <t xml:space="preserve">HERNANDEZ </t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>CASAS</t>
+          <t>CARRIZOSA</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -2265,32 +2261,28 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>5541019261</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>CALLEJON DEL FRESNO 8</t>
-        </is>
-      </c>
+          <t>2217188025</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>09-01-2001</t>
+          <t>13-02-1997</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>GRISELDAROMERO19429@GMAIL.COM</t>
+          <t>OSHESIER77@GMAIL.COM</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>02-03-2026 03:08:05</t>
+          <t>01-03-2026 11:37:19</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -2315,17 +2307,17 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>04-03-2026 03:15:54</t>
+          <t>01-03-2026 11:46:48</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>04-04-2026 23:59:59</t>
+          <t>31-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>04-03-2026 03:12:40</t>
+          <t>01-03-2026 11:46:09</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -2345,14 +2337,10 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>26280522862800008411</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS WEB</t>
-        </is>
-      </c>
+          <t>26280522768240007896</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr"/>
       <c r="Z14" t="inlineStr"/>
       <c r="AA14" t="inlineStr">
         <is>
@@ -2361,7 +2349,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>Christian Yair Peña Villa</t>
+          <t>Josue Radames Rosales Rojas</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2463,7 +2451,7 @@
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>01-04-2026 23:59:59</t>
+          <t>31-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
@@ -2598,7 +2586,7 @@
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>02-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
@@ -2651,12 +2639,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>347674</t>
+          <t>347164</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>89839</t>
+          <t>89329</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2666,17 +2654,17 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>ARMANDO</t>
+          <t>ALMA LIZET</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>ARCOS</t>
+          <t>LUNA</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>MARTINES</t>
+          <t>ARENAS</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2686,7 +2674,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>4811008585</t>
+          <t>5561052467</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2696,22 +2684,22 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>28-08-1997</t>
+          <t>14-10-1975</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>MEDICINAUASLP13@HOTMAIL.COM</t>
+          <t>ALMAARENAS777@GMAIL.COM</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>02-03-2026 16:28:39</t>
+          <t>28-02-2026 09:37:15</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -2726,27 +2714,27 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $649 HE</t>
+          <t>DOMICILIADO PLAN ULTRA PAGO INCIAL 12 MESES $1,549 HE</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>1549</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>02-03-2026 17:40:11</t>
+          <t>03-03-2026 14:29:23</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>02-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>02-03-2026 17:39:26</t>
+          <t>03-03-2026 14:28:32</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2766,22 +2754,18 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>26280522807450008117</t>
+          <t>26280522841740008298</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>Gabriel Pacheco Sanchez</t>
-        </is>
-      </c>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr"/>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>1549</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -2798,12 +2782,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>347446</t>
+          <t>347680</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>89611</t>
+          <t>89845</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2813,17 +2797,17 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>CELIA</t>
+          <t>ARTURO</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t xml:space="preserve">RUIZ </t>
+          <t>HERNANDEZ</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>BAEZ</t>
+          <t>MAGALLON</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2833,28 +2817,28 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>5534529869</t>
+          <t>5610667660</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>03-02-1947</t>
+          <t>14-11-1975</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>BARUCE03@GMAIL.COM</t>
+          <t>HE.MAGALLON@GMAIL.COM</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>02-03-2026 08:33:45</t>
+          <t>02-03-2026 16:35:10</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2869,22 +2853,22 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>ANUALIDAD + MES REGALO $6,999</t>
+          <t>1 MES $999</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>538.38</t>
+          <t>999</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>02-03-2026 15:13:40</t>
+          <t>02-03-2026 16:46:28</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>02-04-2027 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T18" t="inlineStr"/>
@@ -2901,14 +2885,14 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>26280522796960008056</t>
+          <t>26280522803020008099</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr"/>
       <c r="Z18" t="inlineStr"/>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>6999</t>
+          <t>999</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -2925,12 +2909,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>346743</t>
+          <t>347759</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>88908</t>
+          <t>89924</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2940,17 +2924,17 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>ENRIQUE</t>
+          <t>CARLOS</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>GUZMAN</t>
+          <t xml:space="preserve">MARTINEZ </t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>LARA</t>
+          <t>ZARZA</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2960,7 +2944,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>5554577605</t>
+          <t>5517473620</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2975,17 +2959,17 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>14-03-1976</t>
+          <t>24-03-1984</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>EGUZMANL@GMAIL.COM</t>
+          <t>EMZARZA4@GMAIL.COM</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>26-02-2026 16:01:03</t>
+          <t>02-03-2026 17:40:33</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -3010,17 +2994,17 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>02-03-2026 16:33:50</t>
+          <t>02-03-2026 17:52:53</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>02-03-2026 16:32:53</t>
+          <t>02-03-2026 17:52:23</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -3040,14 +3024,10 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>26280522801940008093</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS WEB</t>
-        </is>
-      </c>
+          <t>26280522808850008128</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr"/>
       <c r="Z19" t="inlineStr"/>
       <c r="AA19" t="inlineStr">
         <is>
@@ -3056,12 +3036,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>Christian Yair Peña Villa</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
@@ -3158,7 +3138,7 @@
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
@@ -3207,12 +3187,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>347777</t>
+          <t>347742</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>89942</t>
+          <t>89907</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -3222,17 +3202,17 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>CHRISTIAN IVAN</t>
+          <t xml:space="preserve">VICTOR ALEJANDRO </t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>MERUBIA</t>
+          <t xml:space="preserve">NOVELO </t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>NAVIA</t>
+          <t xml:space="preserve">HERNANDEZ </t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -3242,7 +3222,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>5611521821</t>
+          <t>8134685063</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -3257,17 +3237,17 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>19-10-1992</t>
+          <t>23-09-1997</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>CHRIS_MERUBIA@HOTMAIL.COM</t>
+          <t>VICTORNOVELO97@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>02-03-2026 17:55:56</t>
+          <t>02-03-2026 17:29:11</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -3292,17 +3272,17 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>02-03-2026 19:27:30</t>
+          <t>06-03-2026 17:13:21</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>05-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>02-03-2026 19:26:52</t>
+          <t>06-03-2026 17:12:41</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -3322,15 +3302,19 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>26280522816680008169</t>
+          <t>26280522955730008921</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>PASE 2 DÍAS GRATIS WEB</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr"/>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FANNY ITZEL  VICTORIA  CONTRERAS </t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>649</t>
@@ -3350,12 +3334,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>347583</t>
+          <t>347777</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>89748</t>
+          <t>89942</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3365,17 +3349,17 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>JUAN SALVADOR</t>
+          <t>CHRISTIAN IVAN</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>PEREZ</t>
+          <t>MERUBIA</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>CASTRO</t>
+          <t>NAVIA</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -3385,32 +3369,32 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>5527670454</t>
+          <t>5611521821</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>INSURGENTES SUR</t>
+          <t>TLALPAN</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>23-01-1985</t>
+          <t>19-10-1992</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>JUANITZIO04@GMAIL.COM</t>
+          <t>CHRIS_MERUBIA@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>02-03-2026 14:08:29</t>
+          <t>02-03-2026 17:55:56</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -3425,17 +3409,17 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>DOMICILIADO PLAN ULTRA PAGO INCIAL 12 MESES $1,549 HE</t>
+          <t>DOMICILIADO 12 MESES $649 HE</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>1549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>02-03-2026 14:20:01</t>
+          <t>02-03-2026 19:27:30</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -3445,7 +3429,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>02-03-2026 14:15:35</t>
+          <t>02-03-2026 19:26:52</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -3455,7 +3439,7 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
@@ -3465,36 +3449,40 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>26280522794490008042</t>
-        </is>
-      </c>
-      <c r="Y22" t="inlineStr"/>
+          <t>26280522816680008169</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
       <c r="Z22" t="inlineStr"/>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>1549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Diana Itzel Martinez Colín</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>347557</t>
+          <t>347566</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>89722</t>
+          <t>89731</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3504,17 +3492,17 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>SANTIAGO</t>
+          <t>ERIC</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t xml:space="preserve">MORALES </t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>ALEJANDRO</t>
+          <t>ROMAN</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -3524,10 +3512,14 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>5565099868</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>5540969149</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>TLALPAN</t>
+        </is>
+      </c>
       <c r="J23" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -3535,17 +3527,17 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>19-12-2008</t>
+          <t>08-08-2008</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>ALECOLATE2009@GMAIL.COM</t>
+          <t>ERICSAN08@GMAIL.COM</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>02-03-2026 13:11:52</t>
+          <t>02-03-2026 13:30:16</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -3555,12 +3547,12 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>CONVENIO DOMICILIADO $549</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
@@ -3570,21 +3562,29 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>02-03-2026 15:09:04</t>
+          <t>02-03-2026 13:48:48</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T23" t="inlineStr"/>
+          <t>01-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>02-03-2026 13:45:33</t>
+        </is>
+      </c>
       <c r="U23" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V23" t="inlineStr"/>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W23" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3592,7 +3592,7 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>26280522796610008055</t>
+          <t>26280522793620008038</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr"/>
@@ -3616,12 +3616,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>347613</t>
+          <t>347583</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>89778</t>
+          <t>89748</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3631,30 +3631,34 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>RAQUEL</t>
+          <t>JUAN SALVADOR</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>MONEGRO</t>
+          <t>PEREZ</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>CORDERO</t>
+          <t>CASTRO</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>52</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>1809953468</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>5527670454</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>INSURGENTES SUR</t>
+        </is>
+      </c>
       <c r="J24" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -3662,17 +3666,17 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>28-12-1994</t>
+          <t>23-01-1985</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>MONEGREORAQUEL@GMAIL.COM</t>
+          <t>JUANITZIO04@GMAIL.COM</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>02-03-2026 15:00:46</t>
+          <t>02-03-2026 14:08:29</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -3682,36 +3686,44 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>1 MES $999</t>
+          <t>DOMICILIADO PLAN ULTRA PAGO INCIAL 12 MESES $1,549 HE</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>999</t>
+          <t>1549</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>02-03-2026 15:03:20</t>
+          <t>02-03-2026 14:20:01</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T24" t="inlineStr"/>
+          <t>01-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>02-03-2026 14:15:35</t>
+        </is>
+      </c>
       <c r="U24" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V24" t="inlineStr"/>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W24" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3719,36 +3731,36 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>26280522796360008051</t>
+          <t>26280522794490008042</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr"/>
       <c r="Z24" t="inlineStr"/>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>999</t>
+          <t>1549</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Carlos Arturo Flores Alvarez</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>348179</t>
+          <t>347557</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>90344</t>
+          <t>89722</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3758,17 +3770,17 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">ANDREA </t>
+          <t>SANTIAGO</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t xml:space="preserve">NICOLAS </t>
+          <t xml:space="preserve">MORALES </t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t xml:space="preserve">FLORES </t>
+          <t>ALEJANDRO</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -3778,32 +3790,28 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>5561653454</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>TLALPAN</t>
-        </is>
-      </c>
+          <t>5565099868</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>05-04-1999</t>
+          <t>19-12-2008</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>NIFAANDREA@GMAIL.COM</t>
+          <t>ALECOLATE2009@GMAIL.COM</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>03-03-2026 17:32:31</t>
+          <t>02-03-2026 13:11:52</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -3813,44 +3821,36 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>DOMICILIADO PLAN ULTRA PAGO INCIAL 12 MESES $1,549 HE</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>1549</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>03-03-2026 17:42:08</t>
+          <t>02-03-2026 15:09:04</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T25" t="inlineStr">
-        <is>
-          <t>03-03-2026 17:41:31</t>
-        </is>
-      </c>
+          <t>01-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr"/>
       <c r="U25" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V25" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="V25" t="inlineStr"/>
       <c r="W25" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3858,36 +3858,36 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>26280522851620008359</t>
+          <t>26280522796610008055</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr"/>
       <c r="Z25" t="inlineStr"/>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>1549</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>Diana Itzel Martinez Colín</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>348270</t>
+          <t>347613</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>90435</t>
+          <t>89778</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3897,34 +3897,30 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRENDA </t>
+          <t>RAQUEL</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t xml:space="preserve">VALLE </t>
+          <t>MONEGRO</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t xml:space="preserve">VILLEGAS </t>
+          <t>CORDERO</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>5528942610</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>TLALPAN</t>
-        </is>
-      </c>
+          <t>1809953468</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -3932,17 +3928,17 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>16-04-1998</t>
+          <t>28-12-1994</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>BRE160498V@GMAIL.COM</t>
+          <t>MONEGREORAQUEL@GMAIL.COM</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>03-03-2026 19:31:08</t>
+          <t>02-03-2026 15:00:46</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -3952,44 +3948,36 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $649 HE</t>
+          <t>1 MES $999</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>999</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>03-03-2026 19:40:05</t>
+          <t>02-03-2026 15:03:20</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T26" t="inlineStr">
-        <is>
-          <t>03-03-2026 19:39:01</t>
-        </is>
-      </c>
+          <t>01-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr"/>
       <c r="U26" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V26" t="inlineStr"/>
       <c r="W26" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3997,24 +3985,24 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>26280522859590008403</t>
+          <t>26280522796360008051</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr"/>
       <c r="Z26" t="inlineStr"/>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>999</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Christian Yair Peña Villa</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
@@ -4111,7 +4099,7 @@
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
@@ -4250,7 +4238,7 @@
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
@@ -4299,12 +4287,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>347566</t>
+          <t>348081</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>89731</t>
+          <t>90246</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -4314,17 +4302,17 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>ERIC</t>
+          <t xml:space="preserve">NATALIA </t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t xml:space="preserve">SANCHEZ </t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>ROMAN</t>
+          <t>MENDOZA</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -4334,7 +4322,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>5540969149</t>
+          <t>5545290873</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -4344,22 +4332,22 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>08-08-2008</t>
+          <t>29-08-2007</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>ERICSAN08@GMAIL.COM</t>
+          <t>NATALIAMENDOZA790101@GMAIL.COM</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>02-03-2026 13:30:16</t>
+          <t>03-03-2026 15:19:31</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -4369,22 +4357,22 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>CONVENIO DOMICILIADO $549</t>
+          <t>DOMICILIADO PLAN ULTRA PAGO INCIAL 12 MESES $1,549 HE</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>1549</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>02-03-2026 13:48:48</t>
+          <t>03-03-2026 15:29:19</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
@@ -4394,7 +4382,7 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>02-03-2026 13:45:33</t>
+          <t>03-03-2026 15:28:33</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -4404,7 +4392,7 @@
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W29" t="inlineStr">
@@ -4414,36 +4402,36 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>26280522793620008038</t>
+          <t>26280522843920008315</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr"/>
       <c r="Z29" t="inlineStr"/>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>1549</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Christian Yair Peña Villa</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>348189</t>
+          <t>348134</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>90354</t>
+          <t>90299</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -4453,17 +4441,17 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">MATEO </t>
+          <t>PABLO ANGEL</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t xml:space="preserve">SUAREZ </t>
+          <t xml:space="preserve">CARRILLO </t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t xml:space="preserve">PICHARDO </t>
+          <t>JUAREZ</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -4473,7 +4461,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>5633352915</t>
+          <t>5544502085</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4484,17 +4472,17 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>02-12-2010</t>
+          <t>12-10-1998</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>MATEO.SUAREZ0212@GMAIL.COM</t>
+          <t>PABLOACARRILLOJ@GMAIL.COM</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>03-03-2026 17:44:32</t>
+          <t>03-03-2026 16:49:36</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -4504,12 +4492,12 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>CONVENIO DOMICILIADO $549</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
@@ -4519,29 +4507,21 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>03-03-2026 18:00:56</t>
+          <t>03-03-2026 16:58:26</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T30" t="inlineStr">
-        <is>
-          <t>03-03-2026 18:00:15</t>
-        </is>
-      </c>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr"/>
       <c r="U30" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V30" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="V30" t="inlineStr"/>
       <c r="W30" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4549,7 +4529,7 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>26280522853110008366</t>
+          <t>26280522848750008333</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr"/>
@@ -4573,12 +4553,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>348350</t>
+          <t>348207</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>90515</t>
+          <t>90372</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -4588,17 +4568,17 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>ISMAEL</t>
+          <t>YESELMI EMELIN</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>DIAZ</t>
+          <t xml:space="preserve">BRIVIESCA </t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>GONZALEZ</t>
+          <t xml:space="preserve">MEJIA </t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -4608,32 +4588,28 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>5585277569</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>QUECHOLE</t>
-        </is>
-      </c>
+          <t>5581061114</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>23-10-2010</t>
+          <t>27-08-2007</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>PEDROALCARON9@GMAIL.COM</t>
+          <t>BRIVIESCAYUSLEMI@GMAIL.COM</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>04-03-2026 08:20:20</t>
+          <t>03-03-2026 18:00:26</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -4658,17 +4634,17 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>04-03-2026 08:34:17</t>
+          <t>03-03-2026 18:19:14</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>04-04-2026 23:59:59</t>
+          <t>02-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>04-03-2026 08:33:45</t>
+          <t>03-03-2026 18:18:38</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -4688,7 +4664,7 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>26280522876130008449</t>
+          <t>26280522854400008370</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr"/>
@@ -4700,24 +4676,24 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Diana Itzel Martinez Colín</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>348071</t>
+          <t>347981</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>90236</t>
+          <t>90146</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -4727,17 +4703,17 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>MIGUEL ANGEL</t>
+          <t xml:space="preserve">VALERIA </t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t xml:space="preserve">FUENTES </t>
+          <t>RUIZ</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>AVILA</t>
+          <t>MACIAS</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -4747,32 +4723,32 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>3339470808</t>
+          <t>5571120475</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>TLALPAN</t>
+          <t>COL SAN JUAN DE ARAGON</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>29-09-1982</t>
+          <t>16-07-2004</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>FUENTESAVILA82@YAHOO.COM.MX</t>
+          <t>VALERIA.A.RUIZ@OUTLOOK.COM</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>03-03-2026 14:58:35</t>
+          <t>03-03-2026 09:02:04</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -4787,27 +4763,27 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>RECURRENTE $799 HE</t>
+          <t>CONVENIO DOMICILIADO $549</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>03-03-2026 15:07:01</t>
+          <t>03-03-2026 09:15:14</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>02-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>03-03-2026 15:06:31</t>
+          <t>03-03-2026 09:12:40</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -4827,36 +4803,36 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>26280522843090008308</t>
+          <t>26280522834570008225</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr"/>
       <c r="Z32" t="inlineStr"/>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Josue Radames Rosales Rojas</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>347929</t>
+          <t>348009</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>90094</t>
+          <t>90174</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -4866,17 +4842,17 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>FRANK</t>
+          <t xml:space="preserve">KEVIN </t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>VIGUERAS</t>
+          <t>OSORIA</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>HERNÁNDEZ</t>
+          <t>CORTINAS</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -4886,7 +4862,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>7712142767</t>
+          <t>8662568650</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4897,17 +4873,17 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>17-05-1992</t>
+          <t>11-01-2003</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>VIGUERASFRANK06@GMAIL.COM</t>
+          <t>KEVINOSORIA57@GMAIL.COM</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>03-03-2026 04:45:32</t>
+          <t>03-03-2026 11:14:35</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -4922,22 +4898,22 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>3 MESES $2,099</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>699.67</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>05-03-2026 08:24:41</t>
+          <t>03-03-2026 11:30:05</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>05-06-2026 23:59:59</t>
+          <t>02-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T33" t="inlineStr"/>
@@ -4954,40 +4930,36 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>26280522910670008656</t>
-        </is>
-      </c>
-      <c r="Y33" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS WEB</t>
-        </is>
-      </c>
+          <t>26280522837550008246</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr"/>
       <c r="Z33" t="inlineStr"/>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2099</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Diana Itzel Martinez Colín</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>347759</t>
+          <t>348141</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>89924</t>
+          <t>90306</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -4997,17 +4969,17 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>CARLOS</t>
+          <t>BERTHA MARIA</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t xml:space="preserve">MARTINEZ </t>
+          <t xml:space="preserve">BALDERAS </t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>ZARZA</t>
+          <t>ARENAS</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -5017,32 +4989,28 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>5517473620</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>TLALPAN</t>
-        </is>
-      </c>
+          <t>5554577198</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>24-03-1984</t>
+          <t>17-01-1971</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>EMZARZA4@GMAIL.COM</t>
+          <t>BERTHACAMPERO@YAHOO.COM</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>02-03-2026 17:40:33</t>
+          <t>03-03-2026 17:00:25</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -5057,17 +5025,17 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>DOMICILIADO PLAN ULTRA PAGO INCIAL 12 MESES $1,549 HE</t>
+          <t>DOMICILIADO 12 MESES $649 HE</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>1549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>02-03-2026 17:52:53</t>
+          <t>03-03-2026 17:10:00</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
@@ -5077,7 +5045,7 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>02-03-2026 17:52:23</t>
+          <t>03-03-2026 17:09:07</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -5087,7 +5055,7 @@
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W34" t="inlineStr">
@@ -5097,36 +5065,36 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>26280522808850008128</t>
+          <t>26280522849360008343</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr"/>
       <c r="Z34" t="inlineStr"/>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>1549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Omar Carillo Leal</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>347981</t>
+          <t>348060</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>90146</t>
+          <t>90225</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -5136,17 +5104,17 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">VALERIA </t>
+          <t>FERNANDO MIGUEL</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RUIZ</t>
+          <t>HERNANDEZ</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>MACIAS</t>
+          <t>VILLA</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -5156,32 +5124,32 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>5571120475</t>
+          <t>5516525208</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>COL SAN JUAN DE ARAGON</t>
+          <t>SANTA URSULA</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>16-07-2004</t>
+          <t>13-03-1999</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>VALERIA.A.RUIZ@OUTLOOK.COM</t>
+          <t>FERVILLAH18@GMAIL.COM</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>03-03-2026 09:02:04</t>
+          <t>03-03-2026 14:24:59</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -5191,32 +5159,32 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>CONVENIO DOMICILIADO $549</t>
+          <t>DOMICILIADO 12 MESES $649 HE</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>03-03-2026 09:15:14</t>
+          <t>06-03-2026 14:24:18</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>05-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>03-03-2026 09:12:40</t>
+          <t>06-03-2026 14:21:38</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -5226,7 +5194,7 @@
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W35" t="inlineStr">
@@ -5236,19 +5204,23 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>26280522834570008225</t>
-        </is>
-      </c>
-      <c r="Y35" t="inlineStr"/>
+          <t>26280522950670008890</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
       <c r="Z35" t="inlineStr"/>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>Josue Radames Rosales Rojas</t>
+          <t>Christian Yair Peña Villa</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
@@ -5260,12 +5232,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>347033</t>
+          <t>347929</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>89198</t>
+          <t>90094</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -5275,17 +5247,17 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">VALERIA ALEJANDRA </t>
+          <t>FRANK</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t xml:space="preserve">PADILLA </t>
+          <t>VIGUERAS</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASE </t>
+          <t>HERNÁNDEZ</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -5295,32 +5267,28 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>5512118910</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>TLALPAN</t>
-        </is>
-      </c>
+          <t>7712142767</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>03-02-2006</t>
+          <t>17-05-1992</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>VALERIACASEPER@GMAIL.COM</t>
+          <t>VIGUERASFRANK06@GMAIL.COM</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>27-02-2026 17:40:59</t>
+          <t>03-03-2026 04:45:32</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -5330,44 +5298,36 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>CONVENIO DOMICILIADO $549</t>
+          <t>3 MESES $2,099</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>699.67</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>01-03-2026 13:25:12</t>
+          <t>05-03-2026 08:24:41</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>01-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T36" t="inlineStr">
-        <is>
-          <t>01-03-2026 13:23:47</t>
-        </is>
-      </c>
+          <t>04-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr"/>
       <c r="U36" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V36" t="inlineStr"/>
       <c r="W36" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5375,14 +5335,18 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>26280522769860007910</t>
-        </is>
-      </c>
-      <c r="Y36" t="inlineStr"/>
+          <t>26280522910670008656</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
       <c r="Z36" t="inlineStr"/>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>2099</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
@@ -5399,12 +5363,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>347371</t>
+          <t>348071</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>89536</t>
+          <t>90236</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -5414,17 +5378,17 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>ALBERTO</t>
+          <t>MIGUEL ANGEL</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t xml:space="preserve">ORTIGOZA </t>
+          <t xml:space="preserve">FUENTES </t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>PEREZ</t>
+          <t>AVILA</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -5434,12 +5398,12 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>5649112537</t>
+          <t>3339470808</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>HERRERIAS</t>
+          <t>TLALPAN</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -5449,17 +5413,17 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>14-11-2013</t>
+          <t>29-09-1982</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>ALBERTOOGAZA@GMAIL.COM</t>
+          <t>FUENTESAVILA82@YAHOO.COM.MX</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>02-03-2026 04:30:26</t>
+          <t>03-03-2026 14:58:35</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -5474,17 +5438,17 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>CONVENIO DOMICILIADO $549</t>
+          <t>RECURRENTE $799 HE</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>799</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>02-03-2026 04:40:19</t>
+          <t>03-03-2026 15:07:01</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
@@ -5494,7 +5458,7 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>02-03-2026 04:39:54</t>
+          <t>03-03-2026 15:06:31</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
@@ -5504,7 +5468,7 @@
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W37" t="inlineStr">
@@ -5514,14 +5478,14 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>26280522772000007922</t>
+          <t>26280522843090008308</t>
         </is>
       </c>
       <c r="Y37" t="inlineStr"/>
       <c r="Z37" t="inlineStr"/>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>799</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
@@ -5538,12 +5502,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>348490</t>
+          <t>347482</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>90655</t>
+          <t>89647</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -5553,17 +5517,17 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">JESUS </t>
+          <t>DAVID</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t xml:space="preserve">QUINTANA </t>
+          <t>LLANOS</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t xml:space="preserve">ANDRADE </t>
+          <t>LEGORRETA</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -5573,12 +5537,12 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>6141674674</t>
+          <t>5620518609</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>TLALPAN</t>
+          <t>PLUTARCO ELIAS CALLES</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -5588,17 +5552,17 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>10-03-1999</t>
+          <t>07-04-1974</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>CHUYIN711@GMAIL.COM</t>
+          <t>DAVIDLEGORRETA@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>04-03-2026 16:45:26</t>
+          <t>02-03-2026 10:20:10</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -5613,27 +5577,27 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>DOMICILIADO PLAN ULTRA PAGO INCIAL 12 MESES $1,549 HE</t>
+          <t>DOMICILIADO 12 MESES $649 HE</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>1549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>04-03-2026 16:53:38</t>
+          <t>03-03-2026 04:33:30</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>04-04-2026 23:59:59</t>
+          <t>02-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>04-03-2026 16:52:23</t>
+          <t>03-03-2026 04:29:55</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
@@ -5643,7 +5607,7 @@
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W38" t="inlineStr">
@@ -5653,36 +5617,36 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>26280522888490008569</t>
+          <t>26280522822310008190</t>
         </is>
       </c>
       <c r="Y38" t="inlineStr"/>
       <c r="Z38" t="inlineStr"/>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>1549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Carlos Arturo Flores Alvarez</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>348512</t>
+          <t>347565</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>90677</t>
+          <t>89730</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -5692,17 +5656,17 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>CARLOS ALEXIS</t>
+          <t>JESUS MIGUEL</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>JUAREZ</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>DAVILA</t>
+          <t>VILLEGAS</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -5712,7 +5676,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>5624037947</t>
+          <t>2223618726</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -5727,17 +5691,17 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>07-05-2004</t>
+          <t>07-05-1994</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>CARLOSALEXISMESSI@GMAIL.COM</t>
+          <t>MIGUEL_LV94@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>04-03-2026 17:14:37</t>
+          <t>02-03-2026 13:29:01</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -5752,27 +5716,27 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>CONVENIO DOMICILIADO $549</t>
+          <t>PLAN RECURRENTE PAGO INCIAL $1,549 HE</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>1549</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>04-03-2026 17:24:16</t>
+          <t>02-03-2026 13:35:29</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>04-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>04-03-2026 17:22:45</t>
+          <t>02-03-2026 13:34:42</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -5782,7 +5746,7 @@
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W39" t="inlineStr">
@@ -5792,19 +5756,19 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>26280522890380008587</t>
+          <t>26280522793220008032</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr"/>
       <c r="Z39" t="inlineStr"/>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>1549</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>Carlos Arturo Flores Alvarez</t>
+          <t>Diana Itzel Martinez Colín</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
@@ -5816,12 +5780,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>348009</t>
+          <t>347569</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>90174</t>
+          <t>89734</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -5831,17 +5795,17 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t xml:space="preserve">KEVIN </t>
+          <t>YURIDIA</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>OSORIA</t>
+          <t>ROMAN</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>CORTINAS</t>
+          <t>LAUREL</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -5851,28 +5815,32 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>8662568650</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>7444494140</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>TLALPAN</t>
+        </is>
+      </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>11-01-2003</t>
+          <t>15-09-1972</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>KEVINOSORIA57@GMAIL.COM</t>
+          <t>YURISLIRIS@YAHOO.COM</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>03-03-2026 11:14:35</t>
+          <t>02-03-2026 13:33:31</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -5882,12 +5850,12 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>CONVENIO DOMICILIADO $549</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
@@ -5897,21 +5865,29 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>03-03-2026 11:30:05</t>
+          <t>02-03-2026 13:42:53</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T40" t="inlineStr"/>
+          <t>01-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>02-03-2026 13:40:35</t>
+        </is>
+      </c>
       <c r="U40" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V40" t="inlineStr"/>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W40" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5919,7 +5895,7 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>26280522837550008246</t>
+          <t>26280522793430008035</t>
         </is>
       </c>
       <c r="Y40" t="inlineStr"/>
@@ -5931,24 +5907,24 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>Diana Itzel Martinez Colín</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>348141</t>
+          <t>348273</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>90306</t>
+          <t>90438</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -5958,17 +5934,17 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>BERTHA MARIA</t>
+          <t xml:space="preserve">JERONIMO </t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t xml:space="preserve">BALDERAS </t>
+          <t xml:space="preserve">SOTO </t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>ARENAS</t>
+          <t xml:space="preserve">ORTEGA </t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -5978,28 +5954,32 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>5554577198</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>5567035457</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>TLALPAN</t>
+        </is>
+      </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>17-01-1971</t>
+          <t>12-10-1992</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>BERTHACAMPERO@YAHOO.COM</t>
+          <t>MOMO851245@GMAIL.COM</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>03-03-2026 17:00:25</t>
+          <t>03-03-2026 19:34:21</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -6024,17 +6004,17 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>03-03-2026 17:10:00</t>
+          <t>03-03-2026 19:43:09</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>02-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>03-03-2026 17:09:07</t>
+          <t>03-03-2026 19:42:28</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -6054,7 +6034,7 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>26280522849360008343</t>
+          <t>26280522859660008404</t>
         </is>
       </c>
       <c r="Y41" t="inlineStr"/>
@@ -6066,24 +6046,24 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>Omar Carillo Leal</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>348119</t>
+          <t>348470</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>90284</t>
+          <t>90635</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -6093,17 +6073,17 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t xml:space="preserve">LUIS ARMANDO </t>
+          <t xml:space="preserve">AYLEN GUADALUPE </t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t xml:space="preserve">VILLA </t>
+          <t xml:space="preserve">SALAZAR </t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t xml:space="preserve">CHAVEZ </t>
+          <t xml:space="preserve">RAMIREZ </t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -6113,28 +6093,32 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>6143811757</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>7446933556</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TLALPAN </t>
+        </is>
+      </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>14-06-1995</t>
+          <t>26-08-2002</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>LUISARMANDOVILLAA@GMAIL.COM</t>
+          <t>SALAZARAYLEN0@GMAIL.COM</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>03-03-2026 16:29:37</t>
+          <t>04-03-2026 15:51:49</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -6159,7 +6143,7 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>03-03-2026 16:39:07</t>
+          <t>04-03-2026 16:06:18</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
@@ -6169,7 +6153,7 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>03-03-2026 16:38:32</t>
+          <t>04-03-2026 15:58:52</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
@@ -6179,7 +6163,7 @@
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W42" t="inlineStr">
@@ -6189,7 +6173,7 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>26280522847410008326</t>
+          <t>26280522886430008547</t>
         </is>
       </c>
       <c r="Y42" t="inlineStr"/>
@@ -6213,12 +6197,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>347680</t>
+          <t>348346</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>89845</t>
+          <t>90511</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -6228,17 +6212,17 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>ARTURO</t>
+          <t>JOSUE ABRAHAM</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>HERNANDEZ</t>
+          <t>DIAZ</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>MAGALLON</t>
+          <t>GONZALEZ</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -6248,10 +6232,14 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>5610667660</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>5562030737</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>QUECHOLOC</t>
+        </is>
+      </c>
       <c r="J43" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -6259,17 +6247,17 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>14-11-1975</t>
+          <t>01-09-2006</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>HE.MAGALLON@GMAIL.COM</t>
+          <t>RAY23DIAZ23@GMMAIL.COM</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>02-03-2026 16:35:10</t>
+          <t>04-03-2026 08:18:28</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -6279,36 +6267,44 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>1 MES $999</t>
+          <t>CONVENIO DOMICILIADO $549</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>999</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>02-03-2026 16:46:28</t>
+          <t>04-03-2026 08:33:04</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T43" t="inlineStr"/>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>04-03-2026 08:27:56</t>
+        </is>
+      </c>
       <c r="U43" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V43" t="inlineStr"/>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W43" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -6316,14 +6312,14 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>26280522803020008099</t>
+          <t>26280522876040008448</t>
         </is>
       </c>
       <c r="Y43" t="inlineStr"/>
       <c r="Z43" t="inlineStr"/>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>999</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
@@ -6340,12 +6336,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>348346</t>
+          <t>348384</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>90511</t>
+          <t>90549</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -6355,17 +6351,17 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>JOSUE ABRAHAM</t>
+          <t xml:space="preserve">CAROLINA </t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>DIAZ</t>
+          <t>RIVERA</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>GONZALEZ</t>
+          <t>NIETO</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -6375,32 +6371,32 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>5562030737</t>
+          <t>5548650084</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>QUECHOLOC</t>
+          <t>JOJUTLA</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>01-09-2006</t>
+          <t>10-02-1989</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>RAY23DIAZ23@GMMAIL.COM</t>
+          <t>CARIV1@LIVE.COM.MX</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>04-03-2026 08:18:28</t>
+          <t>04-03-2026 10:42:15</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -6410,32 +6406,32 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>CONVENIO DOMICILIADO $549</t>
+          <t>DOMICILIADO 12 MESES $649 HE</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>04-03-2026 08:33:04</t>
+          <t>04-03-2026 11:08:00</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>04-04-2026 23:59:59</t>
+          <t>03-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>04-03-2026 08:27:56</t>
+          <t>04-03-2026 10:55:20</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
@@ -6455,14 +6451,14 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>26280522876040008448</t>
+          <t>26280522879210008471</t>
         </is>
       </c>
       <c r="Y44" t="inlineStr"/>
       <c r="Z44" t="inlineStr"/>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
@@ -6479,12 +6475,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>348384</t>
+          <t>348490</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>90549</t>
+          <t>90655</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -6494,17 +6490,17 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t xml:space="preserve">CAROLINA </t>
+          <t xml:space="preserve">JESUS </t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>RIVERA</t>
+          <t xml:space="preserve">QUINTANA </t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>NIETO</t>
+          <t xml:space="preserve">ANDRADE </t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -6514,32 +6510,32 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>5548650084</t>
+          <t>6141674674</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>JOJUTLA</t>
+          <t>TLALPAN</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>10-02-1989</t>
+          <t>10-03-1999</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>CARIV1@LIVE.COM.MX</t>
+          <t>CHUYIN711@GMAIL.COM</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>04-03-2026 10:42:15</t>
+          <t>04-03-2026 16:45:26</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -6554,27 +6550,27 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $649 HE</t>
+          <t>DOMICILIADO PLAN ULTRA PAGO INCIAL 12 MESES $1,549 HE</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>1549</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>04-03-2026 11:08:00</t>
+          <t>04-03-2026 16:53:38</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>04-04-2026 23:59:59</t>
+          <t>03-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>04-03-2026 10:55:20</t>
+          <t>04-03-2026 16:52:23</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
@@ -6584,7 +6580,7 @@
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W45" t="inlineStr">
@@ -6594,14 +6590,14 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>26280522879210008471</t>
+          <t>26280522888490008569</t>
         </is>
       </c>
       <c r="Y45" t="inlineStr"/>
       <c r="Z45" t="inlineStr"/>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>1549</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
@@ -6618,12 +6614,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>348081</t>
+          <t>348512</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>90246</t>
+          <t>90677</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -6633,17 +6629,17 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t xml:space="preserve">NATALIA </t>
+          <t>CARLOS ALEXIS</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t xml:space="preserve">SANCHEZ </t>
+          <t>JUAREZ</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>MENDOZA</t>
+          <t>DAVILA</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -6653,7 +6649,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>5545290873</t>
+          <t>5624037947</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -6663,22 +6659,22 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>29-08-2007</t>
+          <t>07-05-2004</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>NATALIAMENDOZA790101@GMAIL.COM</t>
+          <t>CARLOSALEXISMESSI@GMAIL.COM</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>03-03-2026 15:19:31</t>
+          <t>04-03-2026 17:14:37</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -6688,22 +6684,22 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>DOMICILIADO PLAN ULTRA PAGO INCIAL 12 MESES $1,549 HE</t>
+          <t>CONVENIO DOMICILIADO $549</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>1549</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>03-03-2026 15:29:19</t>
+          <t>04-03-2026 17:24:16</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
@@ -6713,7 +6709,7 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>03-03-2026 15:28:33</t>
+          <t>04-03-2026 17:22:45</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
@@ -6723,7 +6719,7 @@
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W46" t="inlineStr">
@@ -6733,36 +6729,36 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>26280522843920008315</t>
+          <t>26280522890380008587</t>
         </is>
       </c>
       <c r="Y46" t="inlineStr"/>
       <c r="Z46" t="inlineStr"/>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>1549</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Carlos Arturo Flores Alvarez</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>348134</t>
+          <t>348189</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>90299</t>
+          <t>90354</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -6772,17 +6768,17 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>PABLO ANGEL</t>
+          <t xml:space="preserve">MATEO </t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t xml:space="preserve">CARRILLO </t>
+          <t xml:space="preserve">SUAREZ </t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>JUAREZ</t>
+          <t xml:space="preserve">PICHARDO </t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -6792,7 +6788,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>5544502085</t>
+          <t>5633352915</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -6803,17 +6799,17 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>12-10-1998</t>
+          <t>02-12-2010</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>PABLOACARRILLOJ@GMAIL.COM</t>
+          <t>MATEO.SUAREZ0212@GMAIL.COM</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>03-03-2026 16:49:36</t>
+          <t>03-03-2026 17:44:32</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -6823,12 +6819,12 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>CONVENIO DOMICILIADO $549</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
@@ -6838,21 +6834,29 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>03-03-2026 16:58:26</t>
+          <t>03-03-2026 18:00:56</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T47" t="inlineStr"/>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>03-03-2026 18:00:15</t>
+        </is>
+      </c>
       <c r="U47" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V47" t="inlineStr"/>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W47" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -6860,7 +6864,7 @@
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>26280522848750008333</t>
+          <t>26280522853110008366</t>
         </is>
       </c>
       <c r="Y47" t="inlineStr"/>
@@ -6884,12 +6888,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>348207</t>
+          <t>348350</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>90372</t>
+          <t>90515</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -6899,17 +6903,17 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>YESELMI EMELIN</t>
+          <t>ISMAEL</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRIVIESCA </t>
+          <t>DIAZ</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t xml:space="preserve">MEJIA </t>
+          <t>GONZALEZ</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -6919,28 +6923,32 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>5581061114</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>5585277569</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>QUECHOLE</t>
+        </is>
+      </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>27-08-2007</t>
+          <t>23-10-2010</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>BRIVIESCAYUSLEMI@GMAIL.COM</t>
+          <t>PEDROALCARON9@GMAIL.COM</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>03-03-2026 18:00:26</t>
+          <t>04-03-2026 08:20:20</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -6965,7 +6973,7 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>03-03-2026 18:19:14</t>
+          <t>04-03-2026 08:34:17</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
@@ -6975,7 +6983,7 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>03-03-2026 18:18:38</t>
+          <t>04-03-2026 08:33:45</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
@@ -6995,7 +7003,7 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>26280522854400008370</t>
+          <t>26280522876130008449</t>
         </is>
       </c>
       <c r="Y48" t="inlineStr"/>
@@ -7007,24 +7015,24 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>Diana Itzel Martinez Colín</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>348273</t>
+          <t>348119</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>90438</t>
+          <t>90284</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -7034,17 +7042,17 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t xml:space="preserve">JERONIMO </t>
+          <t xml:space="preserve">LUIS ARMANDO </t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t xml:space="preserve">SOTO </t>
+          <t xml:space="preserve">VILLA </t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t xml:space="preserve">ORTEGA </t>
+          <t xml:space="preserve">CHAVEZ </t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -7054,14 +7062,10 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>5567035457</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>TLALPAN</t>
-        </is>
-      </c>
+          <t>6143811757</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -7069,17 +7073,17 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>12-10-1992</t>
+          <t>14-06-1995</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>MOMO851245@GMAIL.COM</t>
+          <t>LUISARMANDOVILLAA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>03-03-2026 19:34:21</t>
+          <t>03-03-2026 16:29:37</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -7104,17 +7108,17 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>03-03-2026 19:43:09</t>
+          <t>03-03-2026 16:39:07</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>02-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>03-03-2026 19:42:28</t>
+          <t>03-03-2026 16:38:32</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
@@ -7124,7 +7128,7 @@
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W49" t="inlineStr">
@@ -7134,7 +7138,7 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>26280522859660008404</t>
+          <t>26280522847410008326</t>
         </is>
       </c>
       <c r="Y49" t="inlineStr"/>
@@ -7146,24 +7150,24 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Christian Yair Peña Villa</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>348470</t>
+          <t>348731</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>90635</t>
+          <t>90896</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -7173,17 +7177,17 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t xml:space="preserve">AYLEN GUADALUPE </t>
+          <t xml:space="preserve">RAUL </t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t xml:space="preserve">SALAZAR </t>
+          <t>FERREYRA</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t xml:space="preserve">RAMIREZ </t>
+          <t>ARCOS</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -7193,32 +7197,32 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>7446933556</t>
+          <t>4432655416</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t xml:space="preserve">TLALPAN </t>
+          <t>TLALPAN</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>26-08-2002</t>
+          <t>02-03-1999</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>SALAZARAYLEN0@GMAIL.COM</t>
+          <t>FERRAUL43@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>04-03-2026 15:51:49</t>
+          <t>05-03-2026 15:40:08</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -7233,17 +7237,17 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $649 HE</t>
+          <t>DOMICILIADO PLAN ULTRA PAGO INCIAL 12 MESES $1,549 HE</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>1549</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>04-03-2026 16:06:18</t>
+          <t>05-03-2026 15:48:47</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
@@ -7253,7 +7257,7 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>04-03-2026 15:58:52</t>
+          <t>05-03-2026 15:46:26</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
@@ -7263,7 +7267,7 @@
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W50" t="inlineStr">
@@ -7273,36 +7277,36 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>26280522886430008547</t>
+          <t>26280522919580008735</t>
         </is>
       </c>
       <c r="Y50" t="inlineStr"/>
       <c r="Z50" t="inlineStr"/>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>1549</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>Christian Yair Peña Villa</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>348731</t>
+          <t>348734</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>90896</t>
+          <t>90899</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -7312,17 +7316,17 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t xml:space="preserve">RAUL </t>
+          <t xml:space="preserve">ELIZABETH </t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>FERREYRA</t>
+          <t>ALCALA</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>ARCOS</t>
+          <t>SANJUANICO</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -7332,7 +7336,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>4432655416</t>
+          <t>5535537354</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -7347,17 +7351,17 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>02-03-1999</t>
+          <t>08-01-1968</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>FERRAUL43@HOTMAIL.COM</t>
+          <t>GOR_A@TELMEXMAIL.COM</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>05-03-2026 15:40:08</t>
+          <t>05-03-2026 15:48:40</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -7382,17 +7386,17 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>05-03-2026 15:48:47</t>
+          <t>05-03-2026 16:08:36</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>05-04-2026 23:59:59</t>
+          <t>04-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>05-03-2026 15:46:26</t>
+          <t>05-03-2026 16:05:43</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
@@ -7412,7 +7416,7 @@
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>26280522919580008735</t>
+          <t>26280522920380008738</t>
         </is>
       </c>
       <c r="Y51" t="inlineStr"/>
@@ -7424,24 +7428,24 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Christian Yair Peña Villa</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>348734</t>
+          <t>347674</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>90899</t>
+          <t>89839</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -7451,17 +7455,17 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t xml:space="preserve">ELIZABETH </t>
+          <t>ARMANDO</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>ALCALA</t>
+          <t>ARCOS</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>SANJUANICO</t>
+          <t>MARTINES</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -7471,7 +7475,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>5535537354</t>
+          <t>4811008585</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -7486,17 +7490,17 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>08-01-1968</t>
+          <t>28-08-1997</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>GOR_A@TELMEXMAIL.COM</t>
+          <t>MEDICINAUASLP13@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>05-03-2026 15:48:40</t>
+          <t>02-03-2026 16:28:39</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -7511,64 +7515,489 @@
       </c>
       <c r="P52" t="inlineStr">
         <is>
+          <t>DOMICILIADO 12 MESES $649 HE</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>02-03-2026 17:40:11</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>02-03-2026 17:39:26</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>26280522807450008117</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>Gabriel Pacheco Sanchez</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>348855</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>91020</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>INSURGENTES</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JOSE DIEGO </t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ESPINDOLA </t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GUTIERREZ </t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>5527640385</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>TLALPAN 1</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>28-12-2003</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>JDIEGOHH2812@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>06-03-2026 08:51:37</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 HE</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $649 HE</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>06-03-2026 09:03:11</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>05-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>06-03-2026 09:02:14</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>26280522945130008837</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr"/>
+      <c r="Z53" t="inlineStr"/>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>Josue Radames Rosales Rojas</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>348179</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>90344</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>INSURGENTES</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ANDREA </t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NICOLAS </t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FLORES </t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>5561653454</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>TLALPAN</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>05-04-1999</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>NIFAANDREA@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>03-03-2026 17:32:31</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 HE</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
           <t>DOMICILIADO PLAN ULTRA PAGO INCIAL 12 MESES $1,549 HE</t>
         </is>
       </c>
-      <c r="Q52" t="inlineStr">
+      <c r="Q54" t="inlineStr">
         <is>
           <t>1549</t>
         </is>
       </c>
-      <c r="R52" t="inlineStr">
-        <is>
-          <t>05-03-2026 16:08:36</t>
-        </is>
-      </c>
-      <c r="S52" t="inlineStr">
-        <is>
-          <t>05-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T52" t="inlineStr">
-        <is>
-          <t>05-03-2026 16:05:43</t>
-        </is>
-      </c>
-      <c r="U52" t="inlineStr">
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>03-03-2026 17:42:08</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>03-03-2026 17:41:31</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V52" t="inlineStr">
+      <c r="V54" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="W52" t="inlineStr">
+      <c r="W54" t="inlineStr">
         <is>
           <t>Sucursal</t>
         </is>
       </c>
-      <c r="X52" t="inlineStr">
-        <is>
-          <t>26280522920380008738</t>
-        </is>
-      </c>
-      <c r="Y52" t="inlineStr"/>
-      <c r="Z52" t="inlineStr"/>
-      <c r="AA52" t="inlineStr">
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>26280522851620008359</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr"/>
+      <c r="Z54" t="inlineStr"/>
+      <c r="AA54" t="inlineStr">
         <is>
           <t>1549</t>
         </is>
       </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>Christian Yair Peña Villa</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>Diana Itzel Martinez Colín</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
         <is>
           <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>348270</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>90435</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>INSURGENTES</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BRENDA </t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VALLE </t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VILLEGAS </t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>5528942610</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>TLALPAN</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>16-04-1998</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>BRE160498V@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>03-03-2026 19:31:08</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 HE</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $649 HE</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>03-03-2026 19:40:05</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>03-03-2026 19:39:01</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>26280522859590008403</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr"/>
+      <c r="Z55" t="inlineStr"/>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
